--- a/Solution/PptGeneratorGUI/DataSourceFolder/DataSource.xlsx
+++ b/Solution/PptGeneratorGUI/DataSourceFolder/DataSource.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Lefo\Dev\3 GDPptGenerator\Solution\PptGeneratorGUI\DataSourceFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B61436-B305-4E16-9208-853AD916B30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1708C492-02BF-4C5D-AC79-DB1AE850429B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7860" yWindow="4350" windowWidth="28800" windowHeight="15225" tabRatio="924" firstSheet="9" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="25890" windowHeight="15345" tabRatio="924" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="3" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="338">
   <si>
     <t>FORMULA</t>
   </si>
@@ -909,33 +909,6 @@
     <t>Colonna1</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>A005.01234</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>GD01</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>A005.01234.PK</t>
-  </si>
-  <si>
-    <t>Packer</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>(All)</t>
   </si>
   <si>
@@ -1127,6 +1100,24 @@
   <si>
     <t>D1:L17</t>
   </si>
+  <si>
+    <t>A005.01234_01</t>
+  </si>
+  <si>
+    <t>A005.01234_03</t>
+  </si>
+  <si>
+    <t>A005.01234_05</t>
+  </si>
+  <si>
+    <t>A005.01234_02</t>
+  </si>
+  <si>
+    <t>A005.01234_04</t>
+  </si>
+  <si>
+    <t>A005.01234_06</t>
+  </si>
 </sst>
 </file>
 
@@ -1282,7 +1273,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1479,8 +1470,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="68">
+  <borders count="67">
     <border>
       <left/>
       <right/>
@@ -2300,19 +2303,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2385,7 +2375,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2580,33 +2570,9 @@
     <xf numFmtId="0" fontId="10" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="62" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="63" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="23" borderId="63" xfId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="35" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="63" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="63" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2624,7 +2590,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="67" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="66" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="34" borderId="62" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="35" borderId="62" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="21" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7728,7 +7700,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Michele Fosco" refreshedDate="46009.902117361111" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{CB458B9C-2737-4B20-917D-2647C9E1155E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Michele Fosco" refreshedDate="46155.626948958336" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{CB458B9C-2737-4B20-917D-2647C9E1155E}">
   <cacheSource type="worksheet">
     <worksheetSource name="tabSuperdettagli"/>
   </cacheSource>
@@ -19756,29 +19728,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="142" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
@@ -22841,37 +22813,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="143" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
       <c r="G1" s="66"/>
       <c r="H1" s="66"/>
       <c r="I1" s="66"/>
       <c r="J1" s="66"/>
-      <c r="K1" s="150" t="s">
+      <c r="K1" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="150"/>
+      <c r="L1" s="144"/>
       <c r="M1" s="66"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="149"/>
-      <c r="B2" s="149"/>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
       <c r="G2" s="64"/>
       <c r="H2" s="64"/>
       <c r="I2" s="64"/>
       <c r="J2" s="64"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="150"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
       <c r="M2" s="64"/>
     </row>
     <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -23251,7 +23223,7 @@
         <v>PP_15   Vertical</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65"/>
@@ -23275,7 +23247,7 @@
         <v>PP_16   Vertical</v>
       </c>
       <c r="C20" s="65" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65"/>
@@ -23349,7 +23321,7 @@
         <v>PP_15 PP_07  Vertical</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D23" s="65" t="s">
         <v>117</v>
@@ -23375,7 +23347,7 @@
         <v>PP_16 PP_02  Horizontal</v>
       </c>
       <c r="C24" s="65" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D24" s="65" t="s">
         <v>106</v>
@@ -23509,7 +23481,7 @@
         <v>106</v>
       </c>
       <c r="E29" s="65" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F29" s="87" t="s">
         <v>136</v>
@@ -23537,7 +23509,7 @@
         <v>113</v>
       </c>
       <c r="E30" s="65" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="F30" s="87" t="s">
         <v>136</v>
@@ -24290,10 +24262,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="145" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="146"/>
     </row>
     <row r="2" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="83" t="s">
@@ -24429,10 +24401,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="145" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="152"/>
+      <c r="B1" s="146"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="83" t="s">
@@ -24568,10 +24540,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="147" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="153"/>
+      <c r="B1" s="147"/>
       <c r="C1" s="55"/>
       <c r="D1" s="56"/>
       <c r="E1" s="56"/>
@@ -24748,10 +24720,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="C1" s="107"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -24786,30 +24758,30 @@
       <c r="C6" s="70"/>
     </row>
     <row r="22" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="E22" s="154">
+      <c r="E22" s="148">
         <v>2023</v>
       </c>
-      <c r="F22" s="155"/>
-      <c r="G22" s="154">
+      <c r="F22" s="149"/>
+      <c r="G22" s="148">
         <v>2024</v>
       </c>
-      <c r="H22" s="155"/>
-      <c r="I22" s="160">
+      <c r="H22" s="149"/>
+      <c r="I22" s="154">
         <v>2025</v>
       </c>
-      <c r="J22" s="161"/>
-      <c r="K22" s="162">
+      <c r="J22" s="155"/>
+      <c r="K22" s="156">
         <v>2025</v>
       </c>
-      <c r="L22" s="163"/>
-      <c r="M22" s="154">
+      <c r="L22" s="157"/>
+      <c r="M22" s="148">
         <v>2025</v>
       </c>
-      <c r="N22" s="155"/>
-      <c r="O22" s="156" t="s">
+      <c r="N22" s="149"/>
+      <c r="O22" s="150" t="s">
         <v>164</v>
       </c>
-      <c r="P22" s="157"/>
+      <c r="P22" s="151"/>
     </row>
     <row r="23" spans="4:16" ht="30" x14ac:dyDescent="0.25">
       <c r="D23" s="89"/>
@@ -25411,15 +25383,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -25427,13 +25399,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -25444,86 +25416,86 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G4" t="s">
+        <v>270</v>
+      </c>
+      <c r="H4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I4" t="s">
+        <v>272</v>
+      </c>
+      <c r="J4" t="s">
+        <v>273</v>
+      </c>
+      <c r="K4" t="s">
+        <v>274</v>
+      </c>
+      <c r="L4" t="s">
+        <v>275</v>
+      </c>
+      <c r="M4" t="s">
+        <v>276</v>
+      </c>
+      <c r="N4" t="s">
+        <v>277</v>
+      </c>
+      <c r="O4" t="s">
         <v>278</v>
       </c>
-      <c r="G4" t="s">
+      <c r="P4" t="s">
         <v>279</v>
       </c>
-      <c r="H4" t="s">
+      <c r="Q4" t="s">
         <v>280</v>
-      </c>
-      <c r="I4" t="s">
-        <v>281</v>
-      </c>
-      <c r="J4" t="s">
-        <v>282</v>
-      </c>
-      <c r="K4" t="s">
-        <v>283</v>
-      </c>
-      <c r="L4" t="s">
-        <v>284</v>
-      </c>
-      <c r="M4" t="s">
-        <v>285</v>
-      </c>
-      <c r="N4" t="s">
-        <v>286</v>
-      </c>
-      <c r="O4" t="s">
-        <v>287</v>
-      </c>
-      <c r="P4" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" s="164">
+        <v>298</v>
+      </c>
+      <c r="E5" s="158">
         <v>143530</v>
       </c>
-      <c r="F5" s="164">
+      <c r="F5" s="158">
         <v>14146</v>
       </c>
-      <c r="G5" s="164">
+      <c r="G5" s="158">
         <v>14192</v>
       </c>
-      <c r="H5" s="164">
+      <c r="H5" s="158">
         <v>14238</v>
       </c>
-      <c r="I5" s="164">
+      <c r="I5" s="158">
         <v>14284</v>
       </c>
-      <c r="J5" s="164">
+      <c r="J5" s="158">
         <v>14330</v>
       </c>
-      <c r="K5" s="164">
+      <c r="K5" s="158">
         <v>14376</v>
       </c>
-      <c r="L5" s="164">
+      <c r="L5" s="158">
         <v>14422</v>
       </c>
-      <c r="M5" s="164">
+      <c r="M5" s="158">
         <v>14468</v>
       </c>
-      <c r="N5" s="164">
+      <c r="N5" s="158">
         <v>14514</v>
       </c>
-      <c r="O5" s="164">
+      <c r="O5" s="158">
         <v>14560</v>
       </c>
-      <c r="P5" s="164">
+      <c r="P5" s="158">
         <v>0</v>
       </c>
-      <c r="Q5" s="164">
+      <c r="Q5" s="158">
         <v>0</v>
       </c>
     </row>
@@ -25531,131 +25503,131 @@
       <c r="D6" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>97760</v>
       </c>
-      <c r="F6" s="164">
+      <c r="F6" s="158">
         <v>9632</v>
       </c>
-      <c r="G6" s="164">
+      <c r="G6" s="158">
         <v>9664</v>
       </c>
-      <c r="H6" s="164">
+      <c r="H6" s="158">
         <v>9696</v>
       </c>
-      <c r="I6" s="164">
+      <c r="I6" s="158">
         <v>9728</v>
       </c>
-      <c r="J6" s="164">
+      <c r="J6" s="158">
         <v>9760</v>
       </c>
-      <c r="K6" s="164">
+      <c r="K6" s="158">
         <v>9792</v>
       </c>
-      <c r="L6" s="164">
+      <c r="L6" s="158">
         <v>9824</v>
       </c>
-      <c r="M6" s="164">
+      <c r="M6" s="158">
         <v>9856</v>
       </c>
-      <c r="N6" s="164">
+      <c r="N6" s="158">
         <v>9888</v>
       </c>
-      <c r="O6" s="164">
+      <c r="O6" s="158">
         <v>9920</v>
       </c>
-      <c r="P6" s="164">
+      <c r="P6" s="158">
         <v>0</v>
       </c>
-      <c r="Q6" s="164">
+      <c r="Q6" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D7" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E7" s="164">
+        <v>292</v>
+      </c>
+      <c r="E7" s="158">
         <v>45770</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>4514</v>
       </c>
-      <c r="G7" s="164">
+      <c r="G7" s="158">
         <v>4528</v>
       </c>
-      <c r="H7" s="164">
+      <c r="H7" s="158">
         <v>4542</v>
       </c>
-      <c r="I7" s="164">
+      <c r="I7" s="158">
         <v>4556</v>
       </c>
-      <c r="J7" s="164">
+      <c r="J7" s="158">
         <v>4570</v>
       </c>
-      <c r="K7" s="164">
+      <c r="K7" s="158">
         <v>4584</v>
       </c>
-      <c r="L7" s="164">
+      <c r="L7" s="158">
         <v>4598</v>
       </c>
-      <c r="M7" s="164">
+      <c r="M7" s="158">
         <v>4612</v>
       </c>
-      <c r="N7" s="164">
+      <c r="N7" s="158">
         <v>4626</v>
       </c>
-      <c r="O7" s="164">
+      <c r="O7" s="158">
         <v>4640</v>
       </c>
-      <c r="P7" s="164">
+      <c r="P7" s="158">
         <v>0</v>
       </c>
-      <c r="Q7" s="164">
+      <c r="Q7" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D8" s="70" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="164">
+        <v>299</v>
+      </c>
+      <c r="E8" s="158">
         <v>33605</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>3311</v>
       </c>
-      <c r="G8" s="164">
+      <c r="G8" s="158">
         <v>3322</v>
       </c>
-      <c r="H8" s="164">
+      <c r="H8" s="158">
         <v>3333</v>
       </c>
-      <c r="I8" s="164">
+      <c r="I8" s="158">
         <v>3344</v>
       </c>
-      <c r="J8" s="164">
+      <c r="J8" s="158">
         <v>3355</v>
       </c>
-      <c r="K8" s="164">
+      <c r="K8" s="158">
         <v>3366</v>
       </c>
-      <c r="L8" s="164">
+      <c r="L8" s="158">
         <v>3377</v>
       </c>
-      <c r="M8" s="164">
+      <c r="M8" s="158">
         <v>3388</v>
       </c>
-      <c r="N8" s="164">
+      <c r="N8" s="158">
         <v>3399</v>
       </c>
-      <c r="O8" s="164">
+      <c r="O8" s="158">
         <v>3410</v>
       </c>
-      <c r="P8" s="164">
+      <c r="P8" s="158">
         <v>0</v>
       </c>
-      <c r="Q8" s="164">
+      <c r="Q8" s="158">
         <v>0</v>
       </c>
     </row>
@@ -25663,131 +25635,131 @@
       <c r="D9" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E9" s="164">
+      <c r="E9" s="158">
         <v>13275</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="158">
         <v>1305</v>
       </c>
-      <c r="G9" s="164">
+      <c r="G9" s="158">
         <v>1310</v>
       </c>
-      <c r="H9" s="164">
+      <c r="H9" s="158">
         <v>1315</v>
       </c>
-      <c r="I9" s="164">
+      <c r="I9" s="158">
         <v>1320</v>
       </c>
-      <c r="J9" s="164">
+      <c r="J9" s="158">
         <v>1325</v>
       </c>
-      <c r="K9" s="164">
+      <c r="K9" s="158">
         <v>1330</v>
       </c>
-      <c r="L9" s="164">
+      <c r="L9" s="158">
         <v>1335</v>
       </c>
-      <c r="M9" s="164">
+      <c r="M9" s="158">
         <v>1340</v>
       </c>
-      <c r="N9" s="164">
+      <c r="N9" s="158">
         <v>1345</v>
       </c>
-      <c r="O9" s="164">
+      <c r="O9" s="158">
         <v>1350</v>
       </c>
-      <c r="P9" s="164">
+      <c r="P9" s="158">
         <v>0</v>
       </c>
-      <c r="Q9" s="164">
+      <c r="Q9" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D10" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E10" s="164">
+        <v>292</v>
+      </c>
+      <c r="E10" s="158">
         <v>20330</v>
       </c>
-      <c r="F10" s="164">
+      <c r="F10" s="158">
         <v>2006</v>
       </c>
-      <c r="G10" s="164">
+      <c r="G10" s="158">
         <v>2012</v>
       </c>
-      <c r="H10" s="164">
+      <c r="H10" s="158">
         <v>2018</v>
       </c>
-      <c r="I10" s="164">
+      <c r="I10" s="158">
         <v>2024</v>
       </c>
-      <c r="J10" s="164">
+      <c r="J10" s="158">
         <v>2030</v>
       </c>
-      <c r="K10" s="164">
+      <c r="K10" s="158">
         <v>2036</v>
       </c>
-      <c r="L10" s="164">
+      <c r="L10" s="158">
         <v>2042</v>
       </c>
-      <c r="M10" s="164">
+      <c r="M10" s="158">
         <v>2048</v>
       </c>
-      <c r="N10" s="164">
+      <c r="N10" s="158">
         <v>2054</v>
       </c>
-      <c r="O10" s="164">
+      <c r="O10" s="158">
         <v>2060</v>
       </c>
-      <c r="P10" s="164">
+      <c r="P10" s="158">
         <v>0</v>
       </c>
-      <c r="Q10" s="164">
+      <c r="Q10" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D11" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="E11" s="164">
+        <v>301</v>
+      </c>
+      <c r="E11" s="158">
         <v>22550</v>
       </c>
-      <c r="F11" s="164">
+      <c r="F11" s="158">
         <v>2210</v>
       </c>
-      <c r="G11" s="164">
+      <c r="G11" s="158">
         <v>2220</v>
       </c>
-      <c r="H11" s="164">
+      <c r="H11" s="158">
         <v>2230</v>
       </c>
-      <c r="I11" s="164">
+      <c r="I11" s="158">
         <v>2240</v>
       </c>
-      <c r="J11" s="164">
+      <c r="J11" s="158">
         <v>2250</v>
       </c>
-      <c r="K11" s="164">
+      <c r="K11" s="158">
         <v>2260</v>
       </c>
-      <c r="L11" s="164">
+      <c r="L11" s="158">
         <v>2270</v>
       </c>
-      <c r="M11" s="164">
+      <c r="M11" s="158">
         <v>2280</v>
       </c>
-      <c r="N11" s="164">
+      <c r="N11" s="158">
         <v>2290</v>
       </c>
-      <c r="O11" s="164">
+      <c r="O11" s="158">
         <v>2300</v>
       </c>
-      <c r="P11" s="164">
+      <c r="P11" s="158">
         <v>0</v>
       </c>
-      <c r="Q11" s="164">
+      <c r="Q11" s="158">
         <v>0</v>
       </c>
     </row>
@@ -25795,131 +25767,131 @@
       <c r="D12" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E12" s="164">
+      <c r="E12" s="158">
         <v>14330</v>
       </c>
-      <c r="F12" s="164">
+      <c r="F12" s="158">
         <v>1406</v>
       </c>
-      <c r="G12" s="164">
+      <c r="G12" s="158">
         <v>1412</v>
       </c>
-      <c r="H12" s="164">
+      <c r="H12" s="158">
         <v>1418</v>
       </c>
-      <c r="I12" s="164">
+      <c r="I12" s="158">
         <v>1424</v>
       </c>
-      <c r="J12" s="164">
+      <c r="J12" s="158">
         <v>1430</v>
       </c>
-      <c r="K12" s="164">
+      <c r="K12" s="158">
         <v>1436</v>
       </c>
-      <c r="L12" s="164">
+      <c r="L12" s="158">
         <v>1442</v>
       </c>
-      <c r="M12" s="164">
+      <c r="M12" s="158">
         <v>1448</v>
       </c>
-      <c r="N12" s="164">
+      <c r="N12" s="158">
         <v>1454</v>
       </c>
-      <c r="O12" s="164">
+      <c r="O12" s="158">
         <v>1460</v>
       </c>
-      <c r="P12" s="164">
+      <c r="P12" s="158">
         <v>0</v>
       </c>
-      <c r="Q12" s="164">
+      <c r="Q12" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D13" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E13" s="164">
+        <v>292</v>
+      </c>
+      <c r="E13" s="158">
         <v>8220</v>
       </c>
-      <c r="F13" s="164">
+      <c r="F13" s="158">
         <v>804</v>
       </c>
-      <c r="G13" s="164">
+      <c r="G13" s="158">
         <v>808</v>
       </c>
-      <c r="H13" s="164">
+      <c r="H13" s="158">
         <v>812</v>
       </c>
-      <c r="I13" s="164">
+      <c r="I13" s="158">
         <v>816</v>
       </c>
-      <c r="J13" s="164">
+      <c r="J13" s="158">
         <v>820</v>
       </c>
-      <c r="K13" s="164">
+      <c r="K13" s="158">
         <v>824</v>
       </c>
-      <c r="L13" s="164">
+      <c r="L13" s="158">
         <v>828</v>
       </c>
-      <c r="M13" s="164">
+      <c r="M13" s="158">
         <v>832</v>
       </c>
-      <c r="N13" s="164">
+      <c r="N13" s="158">
         <v>836</v>
       </c>
-      <c r="O13" s="164">
+      <c r="O13" s="158">
         <v>840</v>
       </c>
-      <c r="P13" s="164">
+      <c r="P13" s="158">
         <v>0</v>
       </c>
-      <c r="Q13" s="164">
+      <c r="Q13" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D14" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="164">
+        <v>300</v>
+      </c>
+      <c r="E14" s="158">
         <v>18550</v>
       </c>
-      <c r="F14" s="164">
+      <c r="F14" s="158">
         <v>1810</v>
       </c>
-      <c r="G14" s="164">
+      <c r="G14" s="158">
         <v>1820</v>
       </c>
-      <c r="H14" s="164">
+      <c r="H14" s="158">
         <v>1830</v>
       </c>
-      <c r="I14" s="164">
+      <c r="I14" s="158">
         <v>1840</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="158">
         <v>1850</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="158">
         <v>1860</v>
       </c>
-      <c r="L14" s="164">
+      <c r="L14" s="158">
         <v>1870</v>
       </c>
-      <c r="M14" s="164">
+      <c r="M14" s="158">
         <v>1880</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="158">
         <v>1890</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="158">
         <v>1900</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="158">
         <v>0</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="158">
         <v>0</v>
       </c>
     </row>
@@ -25927,131 +25899,131 @@
       <c r="D15" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E15" s="164">
+      <c r="E15" s="158">
         <v>2055</v>
       </c>
-      <c r="F15" s="164">
+      <c r="F15" s="158">
         <v>201</v>
       </c>
-      <c r="G15" s="164">
+      <c r="G15" s="158">
         <v>202</v>
       </c>
-      <c r="H15" s="164">
+      <c r="H15" s="158">
         <v>203</v>
       </c>
-      <c r="I15" s="164">
+      <c r="I15" s="158">
         <v>204</v>
       </c>
-      <c r="J15" s="164">
+      <c r="J15" s="158">
         <v>205</v>
       </c>
-      <c r="K15" s="164">
+      <c r="K15" s="158">
         <v>206</v>
       </c>
-      <c r="L15" s="164">
+      <c r="L15" s="158">
         <v>207</v>
       </c>
-      <c r="M15" s="164">
+      <c r="M15" s="158">
         <v>208</v>
       </c>
-      <c r="N15" s="164">
+      <c r="N15" s="158">
         <v>209</v>
       </c>
-      <c r="O15" s="164">
+      <c r="O15" s="158">
         <v>210</v>
       </c>
-      <c r="P15" s="164">
+      <c r="P15" s="158">
         <v>0</v>
       </c>
-      <c r="Q15" s="164">
+      <c r="Q15" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D16" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E16" s="164">
+        <v>292</v>
+      </c>
+      <c r="E16" s="158">
         <v>16495</v>
       </c>
-      <c r="F16" s="164">
+      <c r="F16" s="158">
         <v>1609</v>
       </c>
-      <c r="G16" s="164">
+      <c r="G16" s="158">
         <v>1618</v>
       </c>
-      <c r="H16" s="164">
+      <c r="H16" s="158">
         <v>1627</v>
       </c>
-      <c r="I16" s="164">
+      <c r="I16" s="158">
         <v>1636</v>
       </c>
-      <c r="J16" s="164">
+      <c r="J16" s="158">
         <v>1645</v>
       </c>
-      <c r="K16" s="164">
+      <c r="K16" s="158">
         <v>1654</v>
       </c>
-      <c r="L16" s="164">
+      <c r="L16" s="158">
         <v>1663</v>
       </c>
-      <c r="M16" s="164">
+      <c r="M16" s="158">
         <v>1672</v>
       </c>
-      <c r="N16" s="164">
+      <c r="N16" s="158">
         <v>1681</v>
       </c>
-      <c r="O16" s="164">
+      <c r="O16" s="158">
         <v>1690</v>
       </c>
-      <c r="P16" s="164">
+      <c r="P16" s="158">
         <v>0</v>
       </c>
-      <c r="Q16" s="164">
+      <c r="Q16" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D17" s="70" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" s="164">
+        <v>303</v>
+      </c>
+      <c r="E17" s="158">
         <v>13275</v>
       </c>
-      <c r="F17" s="164">
+      <c r="F17" s="158">
         <v>1305</v>
       </c>
-      <c r="G17" s="164">
+      <c r="G17" s="158">
         <v>1310</v>
       </c>
-      <c r="H17" s="164">
+      <c r="H17" s="158">
         <v>1315</v>
       </c>
-      <c r="I17" s="164">
+      <c r="I17" s="158">
         <v>1320</v>
       </c>
-      <c r="J17" s="164">
+      <c r="J17" s="158">
         <v>1325</v>
       </c>
-      <c r="K17" s="164">
+      <c r="K17" s="158">
         <v>1330</v>
       </c>
-      <c r="L17" s="164">
+      <c r="L17" s="158">
         <v>1335</v>
       </c>
-      <c r="M17" s="164">
+      <c r="M17" s="158">
         <v>1340</v>
       </c>
-      <c r="N17" s="164">
+      <c r="N17" s="158">
         <v>1345</v>
       </c>
-      <c r="O17" s="164">
+      <c r="O17" s="158">
         <v>1350</v>
       </c>
-      <c r="P17" s="164">
+      <c r="P17" s="158">
         <v>0</v>
       </c>
-      <c r="Q17" s="164">
+      <c r="Q17" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26059,131 +26031,131 @@
       <c r="D18" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E18" s="164">
+      <c r="E18" s="158">
         <v>4165</v>
       </c>
-      <c r="F18" s="164">
+      <c r="F18" s="158">
         <v>403</v>
       </c>
-      <c r="G18" s="164">
+      <c r="G18" s="158">
         <v>406</v>
       </c>
-      <c r="H18" s="164">
+      <c r="H18" s="158">
         <v>409</v>
       </c>
-      <c r="I18" s="164">
+      <c r="I18" s="158">
         <v>412</v>
       </c>
-      <c r="J18" s="164">
+      <c r="J18" s="158">
         <v>415</v>
       </c>
-      <c r="K18" s="164">
+      <c r="K18" s="158">
         <v>418</v>
       </c>
-      <c r="L18" s="164">
+      <c r="L18" s="158">
         <v>421</v>
       </c>
-      <c r="M18" s="164">
+      <c r="M18" s="158">
         <v>424</v>
       </c>
-      <c r="N18" s="164">
+      <c r="N18" s="158">
         <v>427</v>
       </c>
-      <c r="O18" s="164">
+      <c r="O18" s="158">
         <v>430</v>
       </c>
-      <c r="P18" s="164">
+      <c r="P18" s="158">
         <v>0</v>
       </c>
-      <c r="Q18" s="164">
+      <c r="Q18" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D19" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E19" s="164">
+        <v>292</v>
+      </c>
+      <c r="E19" s="158">
         <v>9110</v>
       </c>
-      <c r="F19" s="164">
+      <c r="F19" s="158">
         <v>902</v>
       </c>
-      <c r="G19" s="164">
+      <c r="G19" s="158">
         <v>904</v>
       </c>
-      <c r="H19" s="164">
+      <c r="H19" s="158">
         <v>906</v>
       </c>
-      <c r="I19" s="164">
+      <c r="I19" s="158">
         <v>908</v>
       </c>
-      <c r="J19" s="164">
+      <c r="J19" s="158">
         <v>910</v>
       </c>
-      <c r="K19" s="164">
+      <c r="K19" s="158">
         <v>912</v>
       </c>
-      <c r="L19" s="164">
+      <c r="L19" s="158">
         <v>914</v>
       </c>
-      <c r="M19" s="164">
+      <c r="M19" s="158">
         <v>916</v>
       </c>
-      <c r="N19" s="164">
+      <c r="N19" s="158">
         <v>918</v>
       </c>
-      <c r="O19" s="164">
+      <c r="O19" s="158">
         <v>920</v>
       </c>
-      <c r="P19" s="164">
+      <c r="P19" s="158">
         <v>0</v>
       </c>
-      <c r="Q19" s="164">
+      <c r="Q19" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D20" s="70" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="164">
+        <v>302</v>
+      </c>
+      <c r="E20" s="158">
         <v>16275</v>
       </c>
-      <c r="F20" s="164">
+      <c r="F20" s="158">
         <v>1605</v>
       </c>
-      <c r="G20" s="164">
+      <c r="G20" s="158">
         <v>1610</v>
       </c>
-      <c r="H20" s="164">
+      <c r="H20" s="158">
         <v>1615</v>
       </c>
-      <c r="I20" s="164">
+      <c r="I20" s="158">
         <v>1620</v>
       </c>
-      <c r="J20" s="164">
+      <c r="J20" s="158">
         <v>1625</v>
       </c>
-      <c r="K20" s="164">
+      <c r="K20" s="158">
         <v>1630</v>
       </c>
-      <c r="L20" s="164">
+      <c r="L20" s="158">
         <v>1635</v>
       </c>
-      <c r="M20" s="164">
+      <c r="M20" s="158">
         <v>1640</v>
       </c>
-      <c r="N20" s="164">
+      <c r="N20" s="158">
         <v>1645</v>
       </c>
-      <c r="O20" s="164">
+      <c r="O20" s="158">
         <v>1650</v>
       </c>
-      <c r="P20" s="164">
+      <c r="P20" s="158">
         <v>0</v>
       </c>
-      <c r="Q20" s="164">
+      <c r="Q20" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26191,131 +26163,131 @@
       <c r="D21" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E21" s="164">
+      <c r="E21" s="158">
         <v>7165</v>
       </c>
-      <c r="F21" s="164">
+      <c r="F21" s="158">
         <v>703</v>
       </c>
-      <c r="G21" s="164">
+      <c r="G21" s="158">
         <v>706</v>
       </c>
-      <c r="H21" s="164">
+      <c r="H21" s="158">
         <v>709</v>
       </c>
-      <c r="I21" s="164">
+      <c r="I21" s="158">
         <v>712</v>
       </c>
-      <c r="J21" s="164">
+      <c r="J21" s="158">
         <v>715</v>
       </c>
-      <c r="K21" s="164">
+      <c r="K21" s="158">
         <v>718</v>
       </c>
-      <c r="L21" s="164">
+      <c r="L21" s="158">
         <v>721</v>
       </c>
-      <c r="M21" s="164">
+      <c r="M21" s="158">
         <v>724</v>
       </c>
-      <c r="N21" s="164">
+      <c r="N21" s="158">
         <v>727</v>
       </c>
-      <c r="O21" s="164">
+      <c r="O21" s="158">
         <v>730</v>
       </c>
-      <c r="P21" s="164">
+      <c r="P21" s="158">
         <v>0</v>
       </c>
-      <c r="Q21" s="164">
+      <c r="Q21" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D22" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E22" s="164">
+        <v>292</v>
+      </c>
+      <c r="E22" s="158">
         <v>9110</v>
       </c>
-      <c r="F22" s="164">
+      <c r="F22" s="158">
         <v>902</v>
       </c>
-      <c r="G22" s="164">
+      <c r="G22" s="158">
         <v>904</v>
       </c>
-      <c r="H22" s="164">
+      <c r="H22" s="158">
         <v>906</v>
       </c>
-      <c r="I22" s="164">
+      <c r="I22" s="158">
         <v>908</v>
       </c>
-      <c r="J22" s="164">
+      <c r="J22" s="158">
         <v>910</v>
       </c>
-      <c r="K22" s="164">
+      <c r="K22" s="158">
         <v>912</v>
       </c>
-      <c r="L22" s="164">
+      <c r="L22" s="158">
         <v>914</v>
       </c>
-      <c r="M22" s="164">
+      <c r="M22" s="158">
         <v>916</v>
       </c>
-      <c r="N22" s="164">
+      <c r="N22" s="158">
         <v>918</v>
       </c>
-      <c r="O22" s="164">
+      <c r="O22" s="158">
         <v>920</v>
       </c>
-      <c r="P22" s="164">
+      <c r="P22" s="158">
         <v>0</v>
       </c>
-      <c r="Q22" s="164">
+      <c r="Q22" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D23" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="E23" s="164">
+        <v>294</v>
+      </c>
+      <c r="E23" s="158">
         <v>1055</v>
       </c>
-      <c r="F23" s="164">
+      <c r="F23" s="158">
         <v>101</v>
       </c>
-      <c r="G23" s="164">
+      <c r="G23" s="158">
         <v>102</v>
       </c>
-      <c r="H23" s="164">
+      <c r="H23" s="158">
         <v>103</v>
       </c>
-      <c r="I23" s="164">
+      <c r="I23" s="158">
         <v>104</v>
       </c>
-      <c r="J23" s="164">
+      <c r="J23" s="158">
         <v>105</v>
       </c>
-      <c r="K23" s="164">
+      <c r="K23" s="158">
         <v>106</v>
       </c>
-      <c r="L23" s="164">
+      <c r="L23" s="158">
         <v>107</v>
       </c>
-      <c r="M23" s="164">
+      <c r="M23" s="158">
         <v>108</v>
       </c>
-      <c r="N23" s="164">
+      <c r="N23" s="158">
         <v>109</v>
       </c>
-      <c r="O23" s="164">
+      <c r="O23" s="158">
         <v>110</v>
       </c>
-      <c r="P23" s="164">
+      <c r="P23" s="158">
         <v>0</v>
       </c>
-      <c r="Q23" s="164">
+      <c r="Q23" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26323,87 +26295,87 @@
       <c r="D24" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E24" s="164">
+      <c r="E24" s="158">
         <v>1055</v>
       </c>
-      <c r="F24" s="164">
+      <c r="F24" s="158">
         <v>101</v>
       </c>
-      <c r="G24" s="164">
+      <c r="G24" s="158">
         <v>102</v>
       </c>
-      <c r="H24" s="164">
+      <c r="H24" s="158">
         <v>103</v>
       </c>
-      <c r="I24" s="164">
+      <c r="I24" s="158">
         <v>104</v>
       </c>
-      <c r="J24" s="164">
+      <c r="J24" s="158">
         <v>105</v>
       </c>
-      <c r="K24" s="164">
+      <c r="K24" s="158">
         <v>106</v>
       </c>
-      <c r="L24" s="164">
+      <c r="L24" s="158">
         <v>107</v>
       </c>
-      <c r="M24" s="164">
+      <c r="M24" s="158">
         <v>108</v>
       </c>
-      <c r="N24" s="164">
+      <c r="N24" s="158">
         <v>109</v>
       </c>
-      <c r="O24" s="164">
+      <c r="O24" s="158">
         <v>110</v>
       </c>
-      <c r="P24" s="164">
+      <c r="P24" s="158">
         <v>0</v>
       </c>
-      <c r="Q24" s="164">
+      <c r="Q24" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D25" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="E25" s="164">
+        <v>293</v>
+      </c>
+      <c r="E25" s="158">
         <v>21495</v>
       </c>
-      <c r="F25" s="164">
+      <c r="F25" s="158">
         <v>2109</v>
       </c>
-      <c r="G25" s="164">
+      <c r="G25" s="158">
         <v>2118</v>
       </c>
-      <c r="H25" s="164">
+      <c r="H25" s="158">
         <v>2127</v>
       </c>
-      <c r="I25" s="164">
+      <c r="I25" s="158">
         <v>2136</v>
       </c>
-      <c r="J25" s="164">
+      <c r="J25" s="158">
         <v>2145</v>
       </c>
-      <c r="K25" s="164">
+      <c r="K25" s="158">
         <v>2154</v>
       </c>
-      <c r="L25" s="164">
+      <c r="L25" s="158">
         <v>2163</v>
       </c>
-      <c r="M25" s="164">
+      <c r="M25" s="158">
         <v>2172</v>
       </c>
-      <c r="N25" s="164">
+      <c r="N25" s="158">
         <v>2181</v>
       </c>
-      <c r="O25" s="164">
+      <c r="O25" s="158">
         <v>2190</v>
       </c>
-      <c r="P25" s="164">
+      <c r="P25" s="158">
         <v>0</v>
       </c>
-      <c r="Q25" s="164">
+      <c r="Q25" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26411,131 +26383,131 @@
       <c r="D26" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E26" s="164">
+      <c r="E26" s="158">
         <v>8110</v>
       </c>
-      <c r="F26" s="164">
+      <c r="F26" s="158">
         <v>802</v>
       </c>
-      <c r="G26" s="164">
+      <c r="G26" s="158">
         <v>804</v>
       </c>
-      <c r="H26" s="164">
+      <c r="H26" s="158">
         <v>806</v>
       </c>
-      <c r="I26" s="164">
+      <c r="I26" s="158">
         <v>808</v>
       </c>
-      <c r="J26" s="164">
+      <c r="J26" s="158">
         <v>810</v>
       </c>
-      <c r="K26" s="164">
+      <c r="K26" s="158">
         <v>812</v>
       </c>
-      <c r="L26" s="164">
+      <c r="L26" s="158">
         <v>814</v>
       </c>
-      <c r="M26" s="164">
+      <c r="M26" s="158">
         <v>816</v>
       </c>
-      <c r="N26" s="164">
+      <c r="N26" s="158">
         <v>818</v>
       </c>
-      <c r="O26" s="164">
+      <c r="O26" s="158">
         <v>820</v>
       </c>
-      <c r="P26" s="164">
+      <c r="P26" s="158">
         <v>0</v>
       </c>
-      <c r="Q26" s="164">
+      <c r="Q26" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D27" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E27" s="164">
+        <v>292</v>
+      </c>
+      <c r="E27" s="158">
         <v>13385</v>
       </c>
-      <c r="F27" s="164">
+      <c r="F27" s="158">
         <v>1307</v>
       </c>
-      <c r="G27" s="164">
+      <c r="G27" s="158">
         <v>1314</v>
       </c>
-      <c r="H27" s="164">
+      <c r="H27" s="158">
         <v>1321</v>
       </c>
-      <c r="I27" s="164">
+      <c r="I27" s="158">
         <v>1328</v>
       </c>
-      <c r="J27" s="164">
+      <c r="J27" s="158">
         <v>1335</v>
       </c>
-      <c r="K27" s="164">
+      <c r="K27" s="158">
         <v>1342</v>
       </c>
-      <c r="L27" s="164">
+      <c r="L27" s="158">
         <v>1349</v>
       </c>
-      <c r="M27" s="164">
+      <c r="M27" s="158">
         <v>1356</v>
       </c>
-      <c r="N27" s="164">
+      <c r="N27" s="158">
         <v>1363</v>
       </c>
-      <c r="O27" s="164">
+      <c r="O27" s="158">
         <v>1370</v>
       </c>
-      <c r="P27" s="164">
+      <c r="P27" s="158">
         <v>0</v>
       </c>
-      <c r="Q27" s="164">
+      <c r="Q27" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D28" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="E28" s="164">
+        <v>296</v>
+      </c>
+      <c r="E28" s="158">
         <v>8110</v>
       </c>
-      <c r="F28" s="164">
+      <c r="F28" s="158">
         <v>802</v>
       </c>
-      <c r="G28" s="164">
+      <c r="G28" s="158">
         <v>804</v>
       </c>
-      <c r="H28" s="164">
+      <c r="H28" s="158">
         <v>806</v>
       </c>
-      <c r="I28" s="164">
+      <c r="I28" s="158">
         <v>808</v>
       </c>
-      <c r="J28" s="164">
+      <c r="J28" s="158">
         <v>810</v>
       </c>
-      <c r="K28" s="164">
+      <c r="K28" s="158">
         <v>812</v>
       </c>
-      <c r="L28" s="164">
+      <c r="L28" s="158">
         <v>814</v>
       </c>
-      <c r="M28" s="164">
+      <c r="M28" s="158">
         <v>816</v>
       </c>
-      <c r="N28" s="164">
+      <c r="N28" s="158">
         <v>818</v>
       </c>
-      <c r="O28" s="164">
+      <c r="O28" s="158">
         <v>820</v>
       </c>
-      <c r="P28" s="164">
+      <c r="P28" s="158">
         <v>0</v>
       </c>
-      <c r="Q28" s="164">
+      <c r="Q28" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26543,175 +26515,175 @@
       <c r="D29" s="110" t="s">
         <v>180</v>
       </c>
-      <c r="E29" s="164">
+      <c r="E29" s="158">
         <v>3055</v>
       </c>
-      <c r="F29" s="164">
+      <c r="F29" s="158">
         <v>301</v>
       </c>
-      <c r="G29" s="164">
+      <c r="G29" s="158">
         <v>302</v>
       </c>
-      <c r="H29" s="164">
+      <c r="H29" s="158">
         <v>303</v>
       </c>
-      <c r="I29" s="164">
+      <c r="I29" s="158">
         <v>304</v>
       </c>
-      <c r="J29" s="164">
+      <c r="J29" s="158">
         <v>305</v>
       </c>
-      <c r="K29" s="164">
+      <c r="K29" s="158">
         <v>306</v>
       </c>
-      <c r="L29" s="164">
+      <c r="L29" s="158">
         <v>307</v>
       </c>
-      <c r="M29" s="164">
+      <c r="M29" s="158">
         <v>308</v>
       </c>
-      <c r="N29" s="164">
+      <c r="N29" s="158">
         <v>309</v>
       </c>
-      <c r="O29" s="164">
+      <c r="O29" s="158">
         <v>310</v>
       </c>
-      <c r="P29" s="164">
+      <c r="P29" s="158">
         <v>0</v>
       </c>
-      <c r="Q29" s="164">
+      <c r="Q29" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D30" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E30" s="164">
+        <v>292</v>
+      </c>
+      <c r="E30" s="158">
         <v>5055</v>
       </c>
-      <c r="F30" s="164">
+      <c r="F30" s="158">
         <v>501</v>
       </c>
-      <c r="G30" s="164">
+      <c r="G30" s="158">
         <v>502</v>
       </c>
-      <c r="H30" s="164">
+      <c r="H30" s="158">
         <v>503</v>
       </c>
-      <c r="I30" s="164">
+      <c r="I30" s="158">
         <v>504</v>
       </c>
-      <c r="J30" s="164">
+      <c r="J30" s="158">
         <v>505</v>
       </c>
-      <c r="K30" s="164">
+      <c r="K30" s="158">
         <v>506</v>
       </c>
-      <c r="L30" s="164">
+      <c r="L30" s="158">
         <v>507</v>
       </c>
-      <c r="M30" s="164">
+      <c r="M30" s="158">
         <v>508</v>
       </c>
-      <c r="N30" s="164">
+      <c r="N30" s="158">
         <v>509</v>
       </c>
-      <c r="O30" s="164">
+      <c r="O30" s="158">
         <v>510</v>
       </c>
-      <c r="P30" s="164">
+      <c r="P30" s="158">
         <v>0</v>
       </c>
-      <c r="Q30" s="164">
+      <c r="Q30" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D31" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="E31" s="164">
+        <v>295</v>
+      </c>
+      <c r="E31" s="158">
         <v>1055</v>
       </c>
-      <c r="F31" s="164">
+      <c r="F31" s="158">
         <v>101</v>
       </c>
-      <c r="G31" s="164">
+      <c r="G31" s="158">
         <v>102</v>
       </c>
-      <c r="H31" s="164">
+      <c r="H31" s="158">
         <v>103</v>
       </c>
-      <c r="I31" s="164">
+      <c r="I31" s="158">
         <v>104</v>
       </c>
-      <c r="J31" s="164">
+      <c r="J31" s="158">
         <v>105</v>
       </c>
-      <c r="K31" s="164">
+      <c r="K31" s="158">
         <v>106</v>
       </c>
-      <c r="L31" s="164">
+      <c r="L31" s="158">
         <v>107</v>
       </c>
-      <c r="M31" s="164">
+      <c r="M31" s="158">
         <v>108</v>
       </c>
-      <c r="N31" s="164">
+      <c r="N31" s="158">
         <v>109</v>
       </c>
-      <c r="O31" s="164">
+      <c r="O31" s="158">
         <v>110</v>
       </c>
-      <c r="P31" s="164">
+      <c r="P31" s="158">
         <v>0</v>
       </c>
-      <c r="Q31" s="164">
+      <c r="Q31" s="158">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D32" s="110" t="s">
-        <v>301</v>
-      </c>
-      <c r="E32" s="164">
+        <v>292</v>
+      </c>
+      <c r="E32" s="158">
         <v>1055</v>
       </c>
-      <c r="F32" s="164">
+      <c r="F32" s="158">
         <v>101</v>
       </c>
-      <c r="G32" s="164">
+      <c r="G32" s="158">
         <v>102</v>
       </c>
-      <c r="H32" s="164">
+      <c r="H32" s="158">
         <v>103</v>
       </c>
-      <c r="I32" s="164">
+      <c r="I32" s="158">
         <v>104</v>
       </c>
-      <c r="J32" s="164">
+      <c r="J32" s="158">
         <v>105</v>
       </c>
-      <c r="K32" s="164">
+      <c r="K32" s="158">
         <v>106</v>
       </c>
-      <c r="L32" s="164">
+      <c r="L32" s="158">
         <v>107</v>
       </c>
-      <c r="M32" s="164">
+      <c r="M32" s="158">
         <v>108</v>
       </c>
-      <c r="N32" s="164">
+      <c r="N32" s="158">
         <v>109</v>
       </c>
-      <c r="O32" s="164">
+      <c r="O32" s="158">
         <v>110</v>
       </c>
-      <c r="P32" s="164">
+      <c r="P32" s="158">
         <v>0</v>
       </c>
-      <c r="Q32" s="164">
+      <c r="Q32" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26719,43 +26691,43 @@
       <c r="D33" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E33" s="164">
+      <c r="E33" s="158">
         <v>279500</v>
       </c>
-      <c r="F33" s="164">
+      <c r="F33" s="158">
         <v>27500</v>
       </c>
-      <c r="G33" s="164">
+      <c r="G33" s="158">
         <v>27600</v>
       </c>
-      <c r="H33" s="164">
+      <c r="H33" s="158">
         <v>27700</v>
       </c>
-      <c r="I33" s="164">
+      <c r="I33" s="158">
         <v>27800</v>
       </c>
-      <c r="J33" s="164">
+      <c r="J33" s="158">
         <v>27900</v>
       </c>
-      <c r="K33" s="164">
+      <c r="K33" s="158">
         <v>28000</v>
       </c>
-      <c r="L33" s="164">
+      <c r="L33" s="158">
         <v>28100</v>
       </c>
-      <c r="M33" s="164">
+      <c r="M33" s="158">
         <v>28200</v>
       </c>
-      <c r="N33" s="164">
+      <c r="N33" s="158">
         <v>28300</v>
       </c>
-      <c r="O33" s="164">
+      <c r="O33" s="158">
         <v>28400</v>
       </c>
-      <c r="P33" s="164">
+      <c r="P33" s="158">
         <v>0</v>
       </c>
-      <c r="Q33" s="164">
+      <c r="Q33" s="158">
         <v>0</v>
       </c>
     </row>
@@ -26777,32 +26749,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="105" t="s">
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="D3" s="134" t="str">
+      <c r="D3" s="126" t="str">
         <f>A4</f>
         <v>Progetti per Engineering unit e project type</v>
       </c>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -26810,70 +26782,70 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="132"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="132"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D8" s="133"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="132"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="132"/>
-      <c r="K8" s="133"/>
-      <c r="L8" s="132"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="125"/>
+      <c r="L8" s="124"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="132"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="124"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="124"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="133"/>
-      <c r="K10" s="133"/>
-      <c r="L10" s="132"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="125"/>
+      <c r="K10" s="125"/>
+      <c r="L10" s="124"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="125"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="133"/>
-      <c r="K12" s="133"/>
-      <c r="L12" s="133"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="125"/>
+      <c r="L12" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -26899,15 +26871,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -26915,13 +26887,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -26929,10 +26901,10 @@
         <v>110</v>
       </c>
       <c r="D4" s="109" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E4" s="109" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -26940,34 +26912,34 @@
         <v>213</v>
       </c>
       <c r="E5" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F5" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="G5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="H5" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="I5" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="J5" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="K5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="L5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="M5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="N5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="O5" t="s">
         <v>214</v>
@@ -26975,75 +26947,75 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D6" s="70" t="s">
-        <v>314</v>
-      </c>
-      <c r="E6" s="164">
+        <v>305</v>
+      </c>
+      <c r="E6" s="158">
         <v>143530</v>
       </c>
-      <c r="F6" s="164">
+      <c r="F6" s="158">
         <v>33605</v>
       </c>
-      <c r="G6" s="164">
+      <c r="G6" s="158">
         <v>18550</v>
       </c>
-      <c r="H6" s="164">
+      <c r="H6" s="158">
         <v>22550</v>
       </c>
-      <c r="I6" s="164">
+      <c r="I6" s="158">
         <v>16275</v>
       </c>
-      <c r="J6" s="164">
+      <c r="J6" s="158">
         <v>13275</v>
       </c>
-      <c r="K6" s="164">
+      <c r="K6" s="158">
         <v>21495</v>
       </c>
-      <c r="L6" s="164">
+      <c r="L6" s="158">
         <v>1055</v>
       </c>
-      <c r="M6" s="164">
+      <c r="M6" s="158">
         <v>1055</v>
       </c>
-      <c r="N6" s="164">
+      <c r="N6" s="158">
         <v>8110</v>
       </c>
-      <c r="O6" s="164">
+      <c r="O6" s="158">
         <v>279500</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D7" s="110"/>
-      <c r="E7" s="164">
+      <c r="E7" s="158">
         <v>143530</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>33605</v>
       </c>
-      <c r="G7" s="164">
+      <c r="G7" s="158">
         <v>18550</v>
       </c>
-      <c r="H7" s="164">
+      <c r="H7" s="158">
         <v>22550</v>
       </c>
-      <c r="I7" s="164">
+      <c r="I7" s="158">
         <v>16275</v>
       </c>
-      <c r="J7" s="164">
+      <c r="J7" s="158">
         <v>13275</v>
       </c>
-      <c r="K7" s="164">
+      <c r="K7" s="158">
         <v>21495</v>
       </c>
-      <c r="L7" s="164">
+      <c r="L7" s="158">
         <v>1055</v>
       </c>
-      <c r="M7" s="164">
+      <c r="M7" s="158">
         <v>1055</v>
       </c>
-      <c r="N7" s="164">
+      <c r="N7" s="158">
         <v>8110</v>
       </c>
-      <c r="O7" s="164">
+      <c r="O7" s="158">
         <v>279500</v>
       </c>
     </row>
@@ -27051,37 +27023,37 @@
       <c r="D8" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="164">
+      <c r="E8" s="158">
         <v>143530</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>33605</v>
       </c>
-      <c r="G8" s="164">
+      <c r="G8" s="158">
         <v>18550</v>
       </c>
-      <c r="H8" s="164">
+      <c r="H8" s="158">
         <v>22550</v>
       </c>
-      <c r="I8" s="164">
+      <c r="I8" s="158">
         <v>16275</v>
       </c>
-      <c r="J8" s="164">
+      <c r="J8" s="158">
         <v>13275</v>
       </c>
-      <c r="K8" s="164">
+      <c r="K8" s="158">
         <v>21495</v>
       </c>
-      <c r="L8" s="164">
+      <c r="L8" s="158">
         <v>1055</v>
       </c>
-      <c r="M8" s="164">
+      <c r="M8" s="158">
         <v>1055</v>
       </c>
-      <c r="N8" s="164">
+      <c r="N8" s="158">
         <v>8110</v>
       </c>
-      <c r="O8" s="164">
+      <c r="O8" s="158">
         <v>279500</v>
       </c>
     </row>
@@ -27106,15 +27078,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -27122,13 +27094,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -27139,14 +27111,14 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
-        <v>320</v>
-      </c>
-      <c r="E5" s="164">
+        <v>311</v>
+      </c>
+      <c r="E5" s="158">
         <v>279500</v>
       </c>
     </row>
@@ -27154,103 +27126,103 @@
       <c r="D6" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>279500</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D7" s="135" t="s">
+      <c r="D7" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="164">
+      <c r="E7" s="158">
         <v>279500</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="136" t="s">
+      <c r="D8" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="164">
+      <c r="E8" s="158">
         <v>279500</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D9" s="137" t="s">
-        <v>307</v>
-      </c>
-      <c r="E9" s="164">
+      <c r="D9" s="129" t="s">
+        <v>298</v>
+      </c>
+      <c r="E9" s="158">
         <v>143530</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D10" s="137" t="s">
-        <v>308</v>
-      </c>
-      <c r="E10" s="164">
+      <c r="D10" s="129" t="s">
+        <v>299</v>
+      </c>
+      <c r="E10" s="158">
         <v>33605</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D11" s="137" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="164">
+      <c r="D11" s="129" t="s">
+        <v>300</v>
+      </c>
+      <c r="E11" s="158">
         <v>18550</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D12" s="137" t="s">
-        <v>310</v>
-      </c>
-      <c r="E12" s="164">
+      <c r="D12" s="129" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="158">
         <v>22550</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="137" t="s">
-        <v>311</v>
-      </c>
-      <c r="E13" s="164">
+      <c r="D13" s="129" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="158">
         <v>16275</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D14" s="137" t="s">
-        <v>312</v>
-      </c>
-      <c r="E14" s="164">
+      <c r="D14" s="129" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="158">
         <v>13275</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D15" s="137" t="s">
-        <v>302</v>
-      </c>
-      <c r="E15" s="164">
+      <c r="D15" s="129" t="s">
+        <v>293</v>
+      </c>
+      <c r="E15" s="158">
         <v>21495</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D16" s="137" t="s">
-        <v>303</v>
-      </c>
-      <c r="E16" s="164">
+      <c r="D16" s="129" t="s">
+        <v>294</v>
+      </c>
+      <c r="E16" s="158">
         <v>1055</v>
       </c>
     </row>
     <row r="17" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D17" s="137" t="s">
-        <v>304</v>
-      </c>
-      <c r="E17" s="164">
+      <c r="D17" s="129" t="s">
+        <v>295</v>
+      </c>
+      <c r="E17" s="158">
         <v>1055</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D18" s="137" t="s">
-        <v>305</v>
-      </c>
-      <c r="E18" s="164">
+      <c r="D18" s="129" t="s">
+        <v>296</v>
+      </c>
+      <c r="E18" s="158">
         <v>8110</v>
       </c>
     </row>
@@ -27258,7 +27230,7 @@
       <c r="D19" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E19" s="164">
+      <c r="E19" s="158">
         <v>279500</v>
       </c>
     </row>
@@ -27305,34 +27277,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="144" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="135"/>
+      <c r="P1" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="145"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="138"/>
+      <c r="T1" s="138"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="139"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
@@ -27520,15 +27492,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -27536,13 +27508,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -27553,14 +27525,14 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="164">
+      <c r="E5" s="158">
         <v>201950</v>
       </c>
     </row>
@@ -27568,13 +27540,13 @@
       <c r="D6" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>201950</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D7" s="135"/>
-      <c r="E7" s="164">
+      <c r="D7" s="127"/>
+      <c r="E7" s="158">
         <v>201950</v>
       </c>
     </row>
@@ -27582,7 +27554,7 @@
       <c r="D8" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="164">
+      <c r="E8" s="158">
         <v>201950</v>
       </c>
     </row>
@@ -27607,15 +27579,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -27623,13 +27595,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -27640,20 +27612,20 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="F4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="164">
+      <c r="E5" s="158">
         <v>201950</v>
       </c>
-      <c r="F5" s="164">
+      <c r="F5" s="158">
         <v>279500</v>
       </c>
     </row>
@@ -27661,230 +27633,230 @@
       <c r="D6" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>201950</v>
       </c>
-      <c r="F6" s="164">
+      <c r="F6" s="158">
         <v>279500</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D7" s="135" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" s="164">
+      <c r="D7" s="127" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" s="158">
         <v>92889</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>143530</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D8" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E8" s="164">
+      <c r="D8" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E8" s="158">
         <v>92889</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>143530</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D9" s="135" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" s="164">
+      <c r="D9" s="127" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="158">
         <v>22225</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="158">
         <v>33605</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D10" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E10" s="164">
+      <c r="D10" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E10" s="158">
         <v>22225</v>
       </c>
-      <c r="F10" s="164">
+      <c r="F10" s="158">
         <v>33605</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="135" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="164">
+      <c r="D11" s="127" t="s">
+        <v>300</v>
+      </c>
+      <c r="E11" s="158">
         <v>20193</v>
       </c>
-      <c r="F11" s="164">
+      <c r="F11" s="158">
         <v>18550</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E12" s="164">
+      <c r="D12" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E12" s="158">
         <v>20193</v>
       </c>
-      <c r="F12" s="164">
+      <c r="F12" s="158">
         <v>18550</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="135" t="s">
-        <v>310</v>
-      </c>
-      <c r="E13" s="164">
+      <c r="D13" s="127" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="158">
         <v>20191</v>
       </c>
-      <c r="F13" s="164">
+      <c r="F13" s="158">
         <v>22550</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E14" s="164">
+      <c r="D14" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E14" s="158">
         <v>20191</v>
       </c>
-      <c r="F14" s="164">
+      <c r="F14" s="158">
         <v>22550</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="135" t="s">
-        <v>311</v>
-      </c>
-      <c r="E15" s="164">
+      <c r="D15" s="127" t="s">
+        <v>302</v>
+      </c>
+      <c r="E15" s="158">
         <v>10103</v>
       </c>
-      <c r="F15" s="164">
+      <c r="F15" s="158">
         <v>16275</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E16" s="164">
+      <c r="D16" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E16" s="158">
         <v>10103</v>
       </c>
-      <c r="F16" s="164">
+      <c r="F16" s="158">
         <v>16275</v>
       </c>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="135" t="s">
-        <v>312</v>
-      </c>
-      <c r="E17" s="164">
+      <c r="D17" s="127" t="s">
+        <v>303</v>
+      </c>
+      <c r="E17" s="158">
         <v>10092</v>
       </c>
-      <c r="F17" s="164">
+      <c r="F17" s="158">
         <v>13275</v>
       </c>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D18" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E18" s="164">
+      <c r="D18" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E18" s="158">
         <v>10092</v>
       </c>
-      <c r="F18" s="164">
+      <c r="F18" s="158">
         <v>13275</v>
       </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D19" s="135" t="s">
-        <v>302</v>
-      </c>
-      <c r="E19" s="164">
+      <c r="D19" s="127" t="s">
+        <v>293</v>
+      </c>
+      <c r="E19" s="158">
         <v>18174</v>
       </c>
-      <c r="F19" s="164">
+      <c r="F19" s="158">
         <v>21495</v>
       </c>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D20" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="164">
+      <c r="D20" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E20" s="158">
         <v>18174</v>
       </c>
-      <c r="F20" s="164">
+      <c r="F20" s="158">
         <v>21495</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="135" t="s">
-        <v>303</v>
-      </c>
-      <c r="E21" s="164">
+      <c r="D21" s="127" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="158">
         <v>2016</v>
       </c>
-      <c r="F21" s="164">
+      <c r="F21" s="158">
         <v>1055</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D22" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E22" s="164">
+      <c r="D22" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" s="158">
         <v>2016</v>
       </c>
-      <c r="F22" s="164">
+      <c r="F22" s="158">
         <v>1055</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="135" t="s">
-        <v>304</v>
-      </c>
-      <c r="E23" s="164">
+      <c r="D23" s="127" t="s">
+        <v>295</v>
+      </c>
+      <c r="E23" s="158">
         <v>2023</v>
       </c>
-      <c r="F23" s="164">
+      <c r="F23" s="158">
         <v>1055</v>
       </c>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D24" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E24" s="164">
+      <c r="D24" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E24" s="158">
         <v>2023</v>
       </c>
-      <c r="F24" s="164">
+      <c r="F24" s="158">
         <v>1055</v>
       </c>
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="135" t="s">
+      <c r="D25" s="127" t="s">
+        <v>296</v>
+      </c>
+      <c r="E25" s="158">
+        <v>4044</v>
+      </c>
+      <c r="F25" s="158">
+        <v>8110</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D26" s="128" t="s">
         <v>305</v>
       </c>
-      <c r="E25" s="164">
+      <c r="E26" s="158">
         <v>4044</v>
       </c>
-      <c r="F25" s="164">
-        <v>8110</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D26" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E26" s="164">
-        <v>4044</v>
-      </c>
-      <c r="F26" s="164">
+      <c r="F26" s="158">
         <v>8110</v>
       </c>
     </row>
@@ -27892,10 +27864,10 @@
       <c r="D27" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="164">
+      <c r="E27" s="158">
         <v>201950</v>
       </c>
-      <c r="F27" s="164">
+      <c r="F27" s="158">
         <v>279500</v>
       </c>
     </row>
@@ -27920,15 +27892,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -27936,13 +27908,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -27953,20 +27925,20 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="164">
+      <c r="E5" s="158">
         <v>201950</v>
       </c>
-      <c r="F5" s="164">
+      <c r="F5" s="158">
         <v>100</v>
       </c>
     </row>
@@ -27974,32 +27946,32 @@
       <c r="D6" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>201950</v>
       </c>
-      <c r="F6" s="164">
+      <c r="F6" s="158">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D7" s="135" t="s">
+      <c r="D7" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="164">
+      <c r="E7" s="158">
         <v>201950</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D8" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E8" s="164">
+      <c r="D8" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E8" s="158">
         <v>201950</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>100</v>
       </c>
     </row>
@@ -28007,10 +27979,10 @@
       <c r="D9" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="164">
+      <c r="E9" s="158">
         <v>201950</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="158">
         <v>100</v>
       </c>
     </row>
@@ -28035,15 +28007,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -28051,13 +28023,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -28068,220 +28040,220 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F4" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
-        <v>314</v>
-      </c>
-      <c r="E5" s="164">
+        <v>305</v>
+      </c>
+      <c r="E5" s="158">
         <v>279500</v>
       </c>
-      <c r="F5" s="164">
+      <c r="F5" s="158">
         <v>27500</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D6" s="110" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" s="164">
+        <v>298</v>
+      </c>
+      <c r="E6" s="158">
         <v>143530</v>
       </c>
-      <c r="F6" s="164">
+      <c r="F6" s="158">
         <v>14146</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D7" s="135"/>
-      <c r="E7" s="164">
+      <c r="D7" s="127"/>
+      <c r="E7" s="158">
         <v>143530</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>14146</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D8" s="110" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="164">
+        <v>299</v>
+      </c>
+      <c r="E8" s="158">
         <v>33605</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>3311</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D9" s="135"/>
-      <c r="E9" s="164">
+      <c r="D9" s="127"/>
+      <c r="E9" s="158">
         <v>33605</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="158">
         <v>3311</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D10" s="110" t="s">
-        <v>309</v>
-      </c>
-      <c r="E10" s="164">
+        <v>300</v>
+      </c>
+      <c r="E10" s="158">
         <v>18550</v>
       </c>
-      <c r="F10" s="164">
+      <c r="F10" s="158">
         <v>1810</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="135"/>
-      <c r="E11" s="164">
+      <c r="D11" s="127"/>
+      <c r="E11" s="158">
         <v>18550</v>
       </c>
-      <c r="F11" s="164">
+      <c r="F11" s="158">
         <v>1810</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D12" s="110" t="s">
-        <v>310</v>
-      </c>
-      <c r="E12" s="164">
+        <v>301</v>
+      </c>
+      <c r="E12" s="158">
         <v>22550</v>
       </c>
-      <c r="F12" s="164">
+      <c r="F12" s="158">
         <v>2210</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="135"/>
-      <c r="E13" s="164">
+      <c r="D13" s="127"/>
+      <c r="E13" s="158">
         <v>22550</v>
       </c>
-      <c r="F13" s="164">
+      <c r="F13" s="158">
         <v>2210</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D14" s="110" t="s">
-        <v>311</v>
-      </c>
-      <c r="E14" s="164">
+        <v>302</v>
+      </c>
+      <c r="E14" s="158">
         <v>16275</v>
       </c>
-      <c r="F14" s="164">
+      <c r="F14" s="158">
         <v>1605</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="135"/>
-      <c r="E15" s="164">
+      <c r="D15" s="127"/>
+      <c r="E15" s="158">
         <v>16275</v>
       </c>
-      <c r="F15" s="164">
+      <c r="F15" s="158">
         <v>1605</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D16" s="110" t="s">
-        <v>312</v>
-      </c>
-      <c r="E16" s="164">
+        <v>303</v>
+      </c>
+      <c r="E16" s="158">
         <v>13275</v>
       </c>
-      <c r="F16" s="164">
+      <c r="F16" s="158">
         <v>1305</v>
       </c>
     </row>
     <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="135"/>
-      <c r="E17" s="164">
+      <c r="D17" s="127"/>
+      <c r="E17" s="158">
         <v>13275</v>
       </c>
-      <c r="F17" s="164">
+      <c r="F17" s="158">
         <v>1305</v>
       </c>
     </row>
     <row r="18" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D18" s="110" t="s">
-        <v>302</v>
-      </c>
-      <c r="E18" s="164">
+        <v>293</v>
+      </c>
+      <c r="E18" s="158">
         <v>21495</v>
       </c>
-      <c r="F18" s="164">
+      <c r="F18" s="158">
         <v>2109</v>
       </c>
     </row>
     <row r="19" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D19" s="135"/>
-      <c r="E19" s="164">
+      <c r="D19" s="127"/>
+      <c r="E19" s="158">
         <v>21495</v>
       </c>
-      <c r="F19" s="164">
+      <c r="F19" s="158">
         <v>2109</v>
       </c>
     </row>
     <row r="20" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D20" s="110" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="164">
+        <v>294</v>
+      </c>
+      <c r="E20" s="158">
         <v>1055</v>
       </c>
-      <c r="F20" s="164">
+      <c r="F20" s="158">
         <v>101</v>
       </c>
     </row>
     <row r="21" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D21" s="135"/>
-      <c r="E21" s="164">
+      <c r="D21" s="127"/>
+      <c r="E21" s="158">
         <v>1055</v>
       </c>
-      <c r="F21" s="164">
+      <c r="F21" s="158">
         <v>101</v>
       </c>
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D22" s="110" t="s">
-        <v>304</v>
-      </c>
-      <c r="E22" s="164">
+        <v>295</v>
+      </c>
+      <c r="E22" s="158">
         <v>1055</v>
       </c>
-      <c r="F22" s="164">
+      <c r="F22" s="158">
         <v>101</v>
       </c>
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D23" s="135"/>
-      <c r="E23" s="164">
+      <c r="D23" s="127"/>
+      <c r="E23" s="158">
         <v>1055</v>
       </c>
-      <c r="F23" s="164">
+      <c r="F23" s="158">
         <v>101</v>
       </c>
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D24" s="110" t="s">
-        <v>305</v>
-      </c>
-      <c r="E24" s="164">
+        <v>296</v>
+      </c>
+      <c r="E24" s="158">
         <v>8110</v>
       </c>
-      <c r="F24" s="164">
+      <c r="F24" s="158">
         <v>802</v>
       </c>
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D25" s="135"/>
-      <c r="E25" s="164">
+      <c r="D25" s="127"/>
+      <c r="E25" s="158">
         <v>8110</v>
       </c>
-      <c r="F25" s="164">
+      <c r="F25" s="158">
         <v>802</v>
       </c>
     </row>
@@ -28289,10 +28261,10 @@
       <c r="D26" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E26" s="164">
+      <c r="E26" s="158">
         <v>279500</v>
       </c>
-      <c r="F26" s="164">
+      <c r="F26" s="158">
         <v>27500</v>
       </c>
     </row>
@@ -28318,15 +28290,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -28334,13 +28306,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -28348,18 +28320,18 @@
         <v>124</v>
       </c>
       <c r="D4" s="109" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E4" s="109" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F5" t="s">
         <v>314</v>
-      </c>
-      <c r="F5" t="s">
-        <v>323</v>
       </c>
       <c r="G5" t="s">
         <v>214</v>
@@ -28370,32 +28342,32 @@
         <v>213</v>
       </c>
       <c r="E6" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D7" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="164">
+      <c r="E7" s="158">
         <v>100</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>100</v>
       </c>
-      <c r="G7" s="164">
+      <c r="G7" s="158">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D8" s="110"/>
-      <c r="E8" s="164">
+      <c r="E8" s="158">
         <v>100</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>100</v>
       </c>
-      <c r="G8" s="164">
+      <c r="G8" s="158">
         <v>100</v>
       </c>
     </row>
@@ -28403,13 +28375,13 @@
       <c r="D9" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E9" s="164">
+      <c r="E9" s="158">
         <v>100</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="158">
         <v>100</v>
       </c>
-      <c r="G9" s="164">
+      <c r="G9" s="158">
         <v>100</v>
       </c>
     </row>
@@ -28433,15 +28405,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -28449,13 +28421,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -28463,7 +28435,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -28476,14 +28448,14 @@
         <v>213</v>
       </c>
       <c r="E5" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D6" s="70" t="s">
-        <v>301</v>
-      </c>
-      <c r="E6" s="164">
+        <v>292</v>
+      </c>
+      <c r="E6" s="158">
         <v>13014</v>
       </c>
     </row>
@@ -28491,23 +28463,23 @@
       <c r="D7" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="164">
+      <c r="E7" s="158">
         <v>13014</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="E8" s="164">
+      <c r="D8" s="127" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="158">
         <v>13014</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D9" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E9" s="164">
+      <c r="D9" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E9" s="158">
         <v>13014</v>
       </c>
     </row>
@@ -28515,7 +28487,7 @@
       <c r="D10" s="70" t="s">
         <v>180</v>
       </c>
-      <c r="E10" s="164">
+      <c r="E10" s="158">
         <v>15286</v>
       </c>
     </row>
@@ -28523,29 +28495,29 @@
       <c r="D11" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="164">
+      <c r="E11" s="158">
         <v>15286</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D12" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="164">
+      <c r="D12" s="127" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="158">
         <v>15286</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="136"/>
-      <c r="E13" s="164">
+      <c r="D13" s="128"/>
+      <c r="E13" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D14" s="136" t="s">
-        <v>314</v>
-      </c>
-      <c r="E14" s="164">
+      <c r="D14" s="128" t="s">
+        <v>305</v>
+      </c>
+      <c r="E14" s="158">
         <v>15277</v>
       </c>
     </row>
@@ -28553,7 +28525,7 @@
       <c r="D15" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="164">
+      <c r="E15" s="158">
         <v>28300</v>
       </c>
     </row>
@@ -28582,15 +28554,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -28598,13 +28570,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -28612,21 +28584,21 @@
         <v>128</v>
       </c>
       <c r="E4" s="109" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="E5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="L5" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="S5" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="T5" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -28678,411 +28650,411 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D7" s="70" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" s="164">
+        <v>298</v>
+      </c>
+      <c r="E7" s="158">
         <v>8</v>
       </c>
-      <c r="F7" s="164">
+      <c r="F7" s="158">
         <v>505</v>
       </c>
-      <c r="G7" s="164">
+      <c r="G7" s="158">
         <v>603</v>
       </c>
-      <c r="H7" s="164">
+      <c r="H7" s="158">
         <v>2709</v>
       </c>
-      <c r="I7" s="164">
+      <c r="I7" s="158">
         <v>3208</v>
       </c>
-      <c r="J7" s="164">
+      <c r="J7" s="158">
         <v>3507</v>
       </c>
-      <c r="K7" s="164">
+      <c r="K7" s="158">
         <v>3606</v>
       </c>
-      <c r="L7" s="164">
+      <c r="L7" s="158">
         <v>16</v>
       </c>
-      <c r="M7" s="164">
+      <c r="M7" s="158">
         <v>510</v>
       </c>
-      <c r="N7" s="164">
+      <c r="N7" s="158">
         <v>606</v>
       </c>
-      <c r="O7" s="164">
+      <c r="O7" s="158">
         <v>2718</v>
       </c>
-      <c r="P7" s="164">
+      <c r="P7" s="158">
         <v>3216</v>
       </c>
-      <c r="Q7" s="164">
+      <c r="Q7" s="158">
         <v>3514</v>
       </c>
-      <c r="R7" s="164">
+      <c r="R7" s="158">
         <v>3612</v>
       </c>
-      <c r="S7" s="164">
+      <c r="S7" s="158">
         <v>14146</v>
       </c>
-      <c r="T7" s="164">
+      <c r="T7" s="158">
         <v>14192</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D8" s="70" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="164">
+        <v>299</v>
+      </c>
+      <c r="E8" s="158">
         <v>1</v>
       </c>
-      <c r="F8" s="164">
+      <c r="F8" s="158">
         <v>101</v>
       </c>
-      <c r="G8" s="164">
+      <c r="G8" s="158">
         <v>804</v>
       </c>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164">
+      <c r="H8" s="158"/>
+      <c r="I8" s="158">
         <v>802</v>
       </c>
-      <c r="J8" s="164">
+      <c r="J8" s="158">
         <v>1002</v>
       </c>
-      <c r="K8" s="164">
+      <c r="K8" s="158">
         <v>601</v>
       </c>
-      <c r="L8" s="164">
+      <c r="L8" s="158">
         <v>2</v>
       </c>
-      <c r="M8" s="164">
+      <c r="M8" s="158">
         <v>102</v>
       </c>
-      <c r="N8" s="164">
+      <c r="N8" s="158">
         <v>808</v>
       </c>
-      <c r="O8" s="164"/>
-      <c r="P8" s="164">
+      <c r="O8" s="158"/>
+      <c r="P8" s="158">
         <v>804</v>
       </c>
-      <c r="Q8" s="164">
+      <c r="Q8" s="158">
         <v>1004</v>
       </c>
-      <c r="R8" s="164">
+      <c r="R8" s="158">
         <v>602</v>
       </c>
-      <c r="S8" s="164">
+      <c r="S8" s="158">
         <v>3311</v>
       </c>
-      <c r="T8" s="164">
+      <c r="T8" s="158">
         <v>3322</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D9" s="70" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="164">
+        <v>300</v>
+      </c>
+      <c r="E9" s="158">
         <v>1</v>
       </c>
-      <c r="F9" s="164">
+      <c r="F9" s="158">
         <v>202</v>
       </c>
-      <c r="G9" s="164">
+      <c r="G9" s="158">
         <v>1005</v>
       </c>
-      <c r="H9" s="164">
+      <c r="H9" s="158">
         <v>602</v>
       </c>
-      <c r="I9" s="164"/>
-      <c r="J9" s="164"/>
-      <c r="K9" s="164"/>
-      <c r="L9" s="164">
+      <c r="I9" s="158"/>
+      <c r="J9" s="158"/>
+      <c r="K9" s="158"/>
+      <c r="L9" s="158">
         <v>2</v>
       </c>
-      <c r="M9" s="164">
+      <c r="M9" s="158">
         <v>204</v>
       </c>
-      <c r="N9" s="164">
+      <c r="N9" s="158">
         <v>1010</v>
       </c>
-      <c r="O9" s="164">
+      <c r="O9" s="158">
         <v>604</v>
       </c>
-      <c r="P9" s="164"/>
-      <c r="Q9" s="164"/>
-      <c r="R9" s="164"/>
-      <c r="S9" s="164">
+      <c r="P9" s="158"/>
+      <c r="Q9" s="158"/>
+      <c r="R9" s="158"/>
+      <c r="S9" s="158">
         <v>1810</v>
       </c>
-      <c r="T9" s="164">
+      <c r="T9" s="158">
         <v>1820</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D10" s="70" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="164">
+        <v>301</v>
+      </c>
+      <c r="E10" s="158">
         <v>1</v>
       </c>
-      <c r="F10" s="164">
+      <c r="F10" s="158">
         <v>404</v>
       </c>
-      <c r="G10" s="164">
+      <c r="G10" s="158">
         <v>402</v>
       </c>
-      <c r="H10" s="164">
+      <c r="H10" s="158">
         <v>301</v>
       </c>
-      <c r="I10" s="164"/>
-      <c r="J10" s="164">
+      <c r="I10" s="158"/>
+      <c r="J10" s="158">
         <v>501</v>
       </c>
-      <c r="K10" s="164">
+      <c r="K10" s="158">
         <v>601</v>
       </c>
-      <c r="L10" s="164">
+      <c r="L10" s="158">
         <v>2</v>
       </c>
-      <c r="M10" s="164">
+      <c r="M10" s="158">
         <v>408</v>
       </c>
-      <c r="N10" s="164">
+      <c r="N10" s="158">
         <v>404</v>
       </c>
-      <c r="O10" s="164">
+      <c r="O10" s="158">
         <v>302</v>
       </c>
-      <c r="P10" s="164"/>
-      <c r="Q10" s="164">
+      <c r="P10" s="158"/>
+      <c r="Q10" s="158">
         <v>502</v>
       </c>
-      <c r="R10" s="164">
+      <c r="R10" s="158">
         <v>602</v>
       </c>
-      <c r="S10" s="164">
+      <c r="S10" s="158">
         <v>2210</v>
       </c>
-      <c r="T10" s="164">
+      <c r="T10" s="158">
         <v>2220</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D11" s="70" t="s">
-        <v>311</v>
-      </c>
-      <c r="E11" s="164">
+        <v>302</v>
+      </c>
+      <c r="E11" s="158">
         <v>1</v>
       </c>
-      <c r="F11" s="164"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164">
+      <c r="F11" s="158"/>
+      <c r="G11" s="158"/>
+      <c r="H11" s="158">
         <v>602</v>
       </c>
-      <c r="I11" s="164">
+      <c r="I11" s="158">
         <v>401</v>
       </c>
-      <c r="J11" s="164"/>
-      <c r="K11" s="164">
+      <c r="J11" s="158"/>
+      <c r="K11" s="158">
         <v>601</v>
       </c>
-      <c r="L11" s="164">
+      <c r="L11" s="158">
         <v>2</v>
       </c>
-      <c r="M11" s="164"/>
-      <c r="N11" s="164"/>
-      <c r="O11" s="164">
+      <c r="M11" s="158"/>
+      <c r="N11" s="158"/>
+      <c r="O11" s="158">
         <v>604</v>
       </c>
-      <c r="P11" s="164">
+      <c r="P11" s="158">
         <v>402</v>
       </c>
-      <c r="Q11" s="164"/>
-      <c r="R11" s="164">
+      <c r="Q11" s="158"/>
+      <c r="R11" s="158">
         <v>602</v>
       </c>
-      <c r="S11" s="164">
+      <c r="S11" s="158">
         <v>1605</v>
       </c>
-      <c r="T11" s="164">
+      <c r="T11" s="158">
         <v>1610</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D12" s="70" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="164">
+        <v>303</v>
+      </c>
+      <c r="E12" s="158">
         <v>2</v>
       </c>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="164">
+      <c r="F12" s="158"/>
+      <c r="G12" s="158"/>
+      <c r="H12" s="158"/>
+      <c r="I12" s="158">
         <v>802</v>
       </c>
-      <c r="J12" s="164">
+      <c r="J12" s="158">
         <v>501</v>
       </c>
-      <c r="K12" s="164"/>
-      <c r="L12" s="164">
+      <c r="K12" s="158"/>
+      <c r="L12" s="158">
         <v>4</v>
       </c>
-      <c r="M12" s="164"/>
-      <c r="N12" s="164"/>
-      <c r="O12" s="164"/>
-      <c r="P12" s="164">
+      <c r="M12" s="158"/>
+      <c r="N12" s="158"/>
+      <c r="O12" s="158"/>
+      <c r="P12" s="158">
         <v>804</v>
       </c>
-      <c r="Q12" s="164">
+      <c r="Q12" s="158">
         <v>502</v>
       </c>
-      <c r="R12" s="164"/>
-      <c r="S12" s="164">
+      <c r="R12" s="158"/>
+      <c r="S12" s="158">
         <v>1305</v>
       </c>
-      <c r="T12" s="164">
+      <c r="T12" s="158">
         <v>1310</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D13" s="70" t="s">
-        <v>302</v>
-      </c>
-      <c r="E13" s="164">
+        <v>293</v>
+      </c>
+      <c r="E13" s="158">
         <v>2</v>
       </c>
-      <c r="F13" s="164">
+      <c r="F13" s="158">
         <v>202</v>
       </c>
-      <c r="G13" s="164">
+      <c r="G13" s="158">
         <v>402</v>
       </c>
-      <c r="H13" s="164"/>
-      <c r="I13" s="164">
+      <c r="H13" s="158"/>
+      <c r="I13" s="158">
         <v>401</v>
       </c>
-      <c r="J13" s="164">
+      <c r="J13" s="158">
         <v>501</v>
       </c>
-      <c r="K13" s="164">
+      <c r="K13" s="158">
         <v>601</v>
       </c>
-      <c r="L13" s="164">
+      <c r="L13" s="158">
         <v>4</v>
       </c>
-      <c r="M13" s="164">
+      <c r="M13" s="158">
         <v>204</v>
       </c>
-      <c r="N13" s="164">
+      <c r="N13" s="158">
         <v>404</v>
       </c>
-      <c r="O13" s="164"/>
-      <c r="P13" s="164">
+      <c r="O13" s="158"/>
+      <c r="P13" s="158">
         <v>402</v>
       </c>
-      <c r="Q13" s="164">
+      <c r="Q13" s="158">
         <v>502</v>
       </c>
-      <c r="R13" s="164">
+      <c r="R13" s="158">
         <v>602</v>
       </c>
-      <c r="S13" s="164">
+      <c r="S13" s="158">
         <v>2109</v>
       </c>
-      <c r="T13" s="164">
+      <c r="T13" s="158">
         <v>2118</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D14" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="E14" s="164"/>
-      <c r="F14" s="164">
+        <v>294</v>
+      </c>
+      <c r="E14" s="158"/>
+      <c r="F14" s="158">
         <v>101</v>
       </c>
-      <c r="G14" s="164"/>
-      <c r="H14" s="164"/>
-      <c r="I14" s="164"/>
-      <c r="J14" s="164"/>
-      <c r="K14" s="164"/>
-      <c r="L14" s="164"/>
-      <c r="M14" s="164">
+      <c r="G14" s="158"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="158"/>
+      <c r="K14" s="158"/>
+      <c r="L14" s="158"/>
+      <c r="M14" s="158">
         <v>102</v>
       </c>
-      <c r="N14" s="164"/>
-      <c r="O14" s="164"/>
-      <c r="P14" s="164"/>
-      <c r="Q14" s="164"/>
-      <c r="R14" s="164"/>
-      <c r="S14" s="164">
+      <c r="N14" s="158"/>
+      <c r="O14" s="158"/>
+      <c r="P14" s="158"/>
+      <c r="Q14" s="158"/>
+      <c r="R14" s="158"/>
+      <c r="S14" s="158">
         <v>101</v>
       </c>
-      <c r="T14" s="164">
+      <c r="T14" s="158">
         <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D15" s="70" t="s">
-        <v>304</v>
-      </c>
-      <c r="E15" s="164"/>
-      <c r="F15" s="164">
+        <v>295</v>
+      </c>
+      <c r="E15" s="158"/>
+      <c r="F15" s="158">
         <v>101</v>
       </c>
-      <c r="G15" s="164"/>
-      <c r="H15" s="164"/>
-      <c r="I15" s="164"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="164"/>
-      <c r="L15" s="164"/>
-      <c r="M15" s="164">
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
+      <c r="K15" s="158"/>
+      <c r="L15" s="158"/>
+      <c r="M15" s="158">
         <v>102</v>
       </c>
-      <c r="N15" s="164"/>
-      <c r="O15" s="164"/>
-      <c r="P15" s="164"/>
-      <c r="Q15" s="164"/>
-      <c r="R15" s="164"/>
-      <c r="S15" s="164">
+      <c r="N15" s="158"/>
+      <c r="O15" s="158"/>
+      <c r="P15" s="158"/>
+      <c r="Q15" s="158"/>
+      <c r="R15" s="158"/>
+      <c r="S15" s="158">
         <v>101</v>
       </c>
-      <c r="T15" s="164">
+      <c r="T15" s="158">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="D16" s="70" t="s">
-        <v>305</v>
-      </c>
-      <c r="E16" s="164"/>
-      <c r="F16" s="164"/>
-      <c r="G16" s="164"/>
-      <c r="H16" s="164">
+        <v>296</v>
+      </c>
+      <c r="E16" s="158"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158">
         <v>301</v>
       </c>
-      <c r="I16" s="164"/>
-      <c r="J16" s="164">
+      <c r="I16" s="158"/>
+      <c r="J16" s="158">
         <v>501</v>
       </c>
-      <c r="K16" s="164"/>
-      <c r="L16" s="164"/>
-      <c r="M16" s="164"/>
-      <c r="N16" s="164"/>
-      <c r="O16" s="164">
+      <c r="K16" s="158"/>
+      <c r="L16" s="158"/>
+      <c r="M16" s="158"/>
+      <c r="N16" s="158"/>
+      <c r="O16" s="158">
         <v>302</v>
       </c>
-      <c r="P16" s="164"/>
-      <c r="Q16" s="164">
+      <c r="P16" s="158"/>
+      <c r="Q16" s="158">
         <v>502</v>
       </c>
-      <c r="R16" s="164"/>
-      <c r="S16" s="164">
+      <c r="R16" s="158"/>
+      <c r="S16" s="158">
         <v>802</v>
       </c>
-      <c r="T16" s="164">
+      <c r="T16" s="158">
         <v>804</v>
       </c>
     </row>
@@ -29090,52 +29062,52 @@
       <c r="D17" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E17" s="164">
+      <c r="E17" s="158">
         <v>16</v>
       </c>
-      <c r="F17" s="164">
+      <c r="F17" s="158">
         <v>1616</v>
       </c>
-      <c r="G17" s="164">
+      <c r="G17" s="158">
         <v>3216</v>
       </c>
-      <c r="H17" s="164">
+      <c r="H17" s="158">
         <v>4515</v>
       </c>
-      <c r="I17" s="164">
+      <c r="I17" s="158">
         <v>5614</v>
       </c>
-      <c r="J17" s="164">
+      <c r="J17" s="158">
         <v>6513</v>
       </c>
-      <c r="K17" s="164">
+      <c r="K17" s="158">
         <v>6010</v>
       </c>
-      <c r="L17" s="164">
+      <c r="L17" s="158">
         <v>32</v>
       </c>
-      <c r="M17" s="164">
+      <c r="M17" s="158">
         <v>1632</v>
       </c>
-      <c r="N17" s="164">
+      <c r="N17" s="158">
         <v>3232</v>
       </c>
-      <c r="O17" s="164">
+      <c r="O17" s="158">
         <v>4530</v>
       </c>
-      <c r="P17" s="164">
+      <c r="P17" s="158">
         <v>5628</v>
       </c>
-      <c r="Q17" s="164">
+      <c r="Q17" s="158">
         <v>6526</v>
       </c>
-      <c r="R17" s="164">
+      <c r="R17" s="158">
         <v>6020</v>
       </c>
-      <c r="S17" s="164">
+      <c r="S17" s="158">
         <v>27500</v>
       </c>
-      <c r="T17" s="164">
+      <c r="T17" s="158">
         <v>27600</v>
       </c>
     </row>
@@ -29159,15 +29131,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -29175,13 +29147,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -29192,14 +29164,14 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="164">
+      <c r="E5" s="158">
         <v>9</v>
       </c>
     </row>
@@ -29207,37 +29179,37 @@
       <c r="D6" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D7" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="E7" s="164">
+      <c r="D7" s="127" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="136" t="s">
+      <c r="D8" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="164">
+      <c r="E8" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D9" s="137"/>
-      <c r="E9" s="164">
+      <c r="D9" s="129"/>
+      <c r="E9" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D10" s="70" t="s">
-        <v>314</v>
-      </c>
-      <c r="E10" s="164">
+        <v>305</v>
+      </c>
+      <c r="E10" s="158">
         <v>28291</v>
       </c>
     </row>
@@ -29245,29 +29217,29 @@
       <c r="D11" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="164">
+      <c r="E11" s="158">
         <v>28291</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D12" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="164">
+      <c r="D12" s="127" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="158">
         <v>28291</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="136" t="s">
+      <c r="D13" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="164">
+      <c r="E13" s="158">
         <v>28291</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D14" s="137"/>
-      <c r="E14" s="164">
+      <c r="D14" s="129"/>
+      <c r="E14" s="158">
         <v>28291</v>
       </c>
     </row>
@@ -29275,7 +29247,7 @@
       <c r="D15" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="164">
+      <c r="E15" s="158">
         <v>28300</v>
       </c>
     </row>
@@ -29299,15 +29271,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
       <c r="D1" s="109" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -29315,13 +29287,13 @@
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D2" s="109" t="s">
         <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -29332,14 +29304,14 @@
         <v>213</v>
       </c>
       <c r="E4" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="164">
+      <c r="E5" s="158">
         <v>9</v>
       </c>
     </row>
@@ -29347,37 +29319,37 @@
       <c r="D6" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="164">
+      <c r="E6" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D7" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="E7" s="164">
+      <c r="D7" s="127" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="136" t="s">
+      <c r="D8" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="164">
+      <c r="E8" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D9" s="137"/>
-      <c r="E9" s="164">
+      <c r="D9" s="129"/>
+      <c r="E9" s="158">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D10" s="70" t="s">
-        <v>314</v>
-      </c>
-      <c r="E10" s="164">
+        <v>305</v>
+      </c>
+      <c r="E10" s="158">
         <v>28291</v>
       </c>
     </row>
@@ -29385,29 +29357,29 @@
       <c r="D11" s="110" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="164">
+      <c r="E11" s="158">
         <v>28291</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D12" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="E12" s="164">
+      <c r="D12" s="127" t="s">
+        <v>311</v>
+      </c>
+      <c r="E12" s="158">
         <v>28291</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D13" s="136" t="s">
+      <c r="D13" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="164">
+      <c r="E13" s="158">
         <v>28291</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D14" s="137"/>
-      <c r="E14" s="164">
+      <c r="D14" s="129"/>
+      <c r="E14" s="158">
         <v>28291</v>
       </c>
     </row>
@@ -29415,7 +29387,7 @@
       <c r="D15" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="164">
+      <c r="E15" s="158">
         <v>28300</v>
       </c>
     </row>
@@ -29437,47 +29409,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="D1" s="131" t="s">
-        <v>336</v>
-      </c>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
+      <c r="B1" s="153"/>
+      <c r="D1" s="123" t="s">
+        <v>327</v>
+      </c>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="105" t="s">
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>335</v>
-      </c>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
+        <v>326</v>
+      </c>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="123"/>
+      <c r="F4" s="123"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D5" s="131"/>
-      <c r="E5" s="131"/>
-      <c r="F5" s="131"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131" t="s">
-        <v>334</v>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -29590,94 +29562,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
+      <c r="B1" s="153"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="105" t="s">
         <v>161</v>
       </c>
       <c r="B2" s="106" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
+        <v>328</v>
+      </c>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
     </row>
     <row r="3" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
     </row>
     <row r="4" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
     </row>
     <row r="5" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="138"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="138"/>
-      <c r="E8" s="138"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
     </row>
     <row r="9" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="130"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
     </row>
     <row r="10" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D10" s="138"/>
-      <c r="E10" s="138"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="130"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -29698,10 +29670,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="152" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="159"/>
+      <c r="B1" s="153"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="105" t="s">
@@ -29817,98 +29789,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:82" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
-      <c r="Z1" s="140"/>
-      <c r="AA1" s="140"/>
-      <c r="AB1" s="140"/>
-      <c r="AC1" s="140"/>
-      <c r="AD1" s="141"/>
-      <c r="AE1" s="146" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="135"/>
+      <c r="AE1" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="AF1" s="147"/>
-      <c r="AG1" s="147"/>
-      <c r="AH1" s="147"/>
-      <c r="AI1" s="147"/>
-      <c r="AJ1" s="147"/>
-      <c r="AK1" s="147"/>
-      <c r="AL1" s="147"/>
-      <c r="AM1" s="147"/>
-      <c r="AN1" s="147"/>
-      <c r="AO1" s="147"/>
-      <c r="AP1" s="147"/>
-      <c r="AQ1" s="147"/>
-      <c r="AR1" s="147"/>
-      <c r="AS1" s="147"/>
-      <c r="AT1" s="147"/>
-      <c r="AU1" s="147"/>
-      <c r="AV1" s="147"/>
-      <c r="AW1" s="147"/>
-      <c r="AX1" s="147"/>
-      <c r="AY1" s="147"/>
-      <c r="AZ1" s="147"/>
-      <c r="BA1" s="147"/>
-      <c r="BB1" s="147"/>
-      <c r="BC1" s="147"/>
-      <c r="BD1" s="147"/>
-      <c r="BE1" s="147"/>
-      <c r="BF1" s="147"/>
-      <c r="BG1" s="147"/>
-      <c r="BH1" s="147"/>
-      <c r="BI1" s="147"/>
-      <c r="BJ1" s="147"/>
-      <c r="BK1" s="147"/>
-      <c r="BL1" s="147"/>
-      <c r="BM1" s="147"/>
-      <c r="BN1" s="147"/>
-      <c r="BO1" s="147"/>
-      <c r="BP1" s="147"/>
-      <c r="BQ1" s="147"/>
-      <c r="BR1" s="147"/>
-      <c r="BS1" s="147"/>
-      <c r="BT1" s="147"/>
-      <c r="BU1" s="147"/>
-      <c r="BV1" s="147"/>
-      <c r="BW1" s="147"/>
-      <c r="BX1" s="147"/>
-      <c r="BY1" s="147"/>
-      <c r="BZ1" s="147"/>
-      <c r="CA1" s="147"/>
-      <c r="CB1" s="147"/>
-      <c r="CC1" s="147"/>
-      <c r="CD1" s="148"/>
+      <c r="AF1" s="141"/>
+      <c r="AG1" s="141"/>
+      <c r="AH1" s="141"/>
+      <c r="AI1" s="141"/>
+      <c r="AJ1" s="141"/>
+      <c r="AK1" s="141"/>
+      <c r="AL1" s="141"/>
+      <c r="AM1" s="141"/>
+      <c r="AN1" s="141"/>
+      <c r="AO1" s="141"/>
+      <c r="AP1" s="141"/>
+      <c r="AQ1" s="141"/>
+      <c r="AR1" s="141"/>
+      <c r="AS1" s="141"/>
+      <c r="AT1" s="141"/>
+      <c r="AU1" s="141"/>
+      <c r="AV1" s="141"/>
+      <c r="AW1" s="141"/>
+      <c r="AX1" s="141"/>
+      <c r="AY1" s="141"/>
+      <c r="AZ1" s="141"/>
+      <c r="BA1" s="141"/>
+      <c r="BB1" s="141"/>
+      <c r="BC1" s="141"/>
+      <c r="BD1" s="141"/>
+      <c r="BE1" s="141"/>
+      <c r="BF1" s="141"/>
+      <c r="BG1" s="141"/>
+      <c r="BH1" s="141"/>
+      <c r="BI1" s="141"/>
+      <c r="BJ1" s="141"/>
+      <c r="BK1" s="141"/>
+      <c r="BL1" s="141"/>
+      <c r="BM1" s="141"/>
+      <c r="BN1" s="141"/>
+      <c r="BO1" s="141"/>
+      <c r="BP1" s="141"/>
+      <c r="BQ1" s="141"/>
+      <c r="BR1" s="141"/>
+      <c r="BS1" s="141"/>
+      <c r="BT1" s="141"/>
+      <c r="BU1" s="141"/>
+      <c r="BV1" s="141"/>
+      <c r="BW1" s="141"/>
+      <c r="BX1" s="141"/>
+      <c r="BY1" s="141"/>
+      <c r="BZ1" s="141"/>
+      <c r="CA1" s="141"/>
+      <c r="CB1" s="141"/>
+      <c r="CC1" s="141"/>
+      <c r="CD1" s="142"/>
     </row>
     <row r="2" spans="1:82" s="1" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A2" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="121" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="117" t="s">
@@ -29971,7 +29943,7 @@
       <c r="V2" s="117" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="129" t="s">
+      <c r="W2" s="121" t="s">
         <v>65</v>
       </c>
       <c r="X2" s="117" t="s">
@@ -30268,16 +30240,16 @@
         <v/>
       </c>
       <c r="AE3" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP3" t="s">
         <v>180</v>
       </c>
       <c r="AQ3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ3">
         <v>1</v>
@@ -30312,13 +30284,13 @@
       <c r="BV3">
         <v>55</v>
       </c>
-      <c r="BX3" s="130">
+      <c r="BX3" s="122">
         <v>42006</v>
       </c>
-      <c r="CB3" s="130">
+      <c r="CB3" s="122">
         <v>42005</v>
       </c>
-      <c r="CC3" s="130">
+      <c r="CC3" s="122">
         <v>42045</v>
       </c>
     </row>
@@ -30439,16 +30411,16 @@
         <v/>
       </c>
       <c r="AE4" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP4" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ4" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV4" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ4">
         <v>101</v>
@@ -30483,13 +30455,13 @@
       <c r="BV4">
         <v>1055</v>
       </c>
-      <c r="BX4" s="130">
+      <c r="BX4" s="122">
         <v>42009</v>
       </c>
-      <c r="CB4" s="130">
+      <c r="CB4" s="122">
         <v>42008</v>
       </c>
-      <c r="CC4" s="130">
+      <c r="CC4" s="122">
         <v>42048</v>
       </c>
     </row>
@@ -30610,16 +30582,16 @@
         <v/>
       </c>
       <c r="AE5" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP5" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ5" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ5">
         <v>201</v>
@@ -30654,13 +30626,13 @@
       <c r="BV5">
         <v>2055</v>
       </c>
-      <c r="BX5" s="130">
+      <c r="BX5" s="122">
         <v>42012</v>
       </c>
-      <c r="CB5" s="130">
+      <c r="CB5" s="122">
         <v>42011</v>
       </c>
-      <c r="CC5" s="130">
+      <c r="CC5" s="122">
         <v>42051</v>
       </c>
     </row>
@@ -30781,16 +30753,16 @@
         <v/>
       </c>
       <c r="AE6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP6" t="s">
         <v>180</v>
       </c>
       <c r="AQ6" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV6" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ6">
         <v>1</v>
@@ -30825,13 +30797,13 @@
       <c r="BV6">
         <v>55</v>
       </c>
-      <c r="BX6" s="130">
+      <c r="BX6" s="122">
         <v>42015</v>
       </c>
-      <c r="CB6" s="130">
+      <c r="CB6" s="122">
         <v>42014</v>
       </c>
-      <c r="CC6" s="130">
+      <c r="CC6" s="122">
         <v>42054</v>
       </c>
     </row>
@@ -30952,16 +30924,16 @@
         <v/>
       </c>
       <c r="AE7" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP7" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ7" t="s">
         <v>301</v>
       </c>
-      <c r="AQ7" t="s">
-        <v>310</v>
-      </c>
       <c r="AV7" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ7">
         <v>101</v>
@@ -30996,13 +30968,13 @@
       <c r="BV7">
         <v>1055</v>
       </c>
-      <c r="BX7" s="130">
+      <c r="BX7" s="122">
         <v>42018</v>
       </c>
-      <c r="CB7" s="130">
+      <c r="CB7" s="122">
         <v>42017</v>
       </c>
-      <c r="CC7" s="130">
+      <c r="CC7" s="122">
         <v>42057</v>
       </c>
     </row>
@@ -31123,16 +31095,16 @@
         <v/>
       </c>
       <c r="AE8" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ8" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV8" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ8">
         <v>201</v>
@@ -31167,13 +31139,13 @@
       <c r="BV8">
         <v>2055</v>
       </c>
-      <c r="BX8" s="130">
+      <c r="BX8" s="122">
         <v>42021</v>
       </c>
-      <c r="CB8" s="130">
+      <c r="CB8" s="122">
         <v>42020</v>
       </c>
-      <c r="CC8" s="130">
+      <c r="CC8" s="122">
         <v>42060</v>
       </c>
     </row>
@@ -31294,16 +31266,16 @@
         <v/>
       </c>
       <c r="AE9" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP9" t="s">
         <v>180</v>
       </c>
       <c r="AQ9" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV9" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ9">
         <v>301</v>
@@ -31338,13 +31310,13 @@
       <c r="BV9">
         <v>3055</v>
       </c>
-      <c r="BX9" s="130">
+      <c r="BX9" s="122">
         <v>42024</v>
       </c>
-      <c r="CB9" s="130">
+      <c r="CB9" s="122">
         <v>42023</v>
       </c>
-      <c r="CC9" s="130">
+      <c r="CC9" s="122">
         <v>42063</v>
       </c>
     </row>
@@ -31465,16 +31437,16 @@
         <v/>
       </c>
       <c r="AE10" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP10" t="s">
         <v>180</v>
       </c>
       <c r="AQ10" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AV10" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ10">
         <v>401</v>
@@ -31509,13 +31481,13 @@
       <c r="BV10">
         <v>4055</v>
       </c>
-      <c r="BX10" s="130">
+      <c r="BX10" s="122">
         <v>42027</v>
       </c>
-      <c r="CB10" s="130">
+      <c r="CB10" s="122">
         <v>42026</v>
       </c>
-      <c r="CC10" s="130">
+      <c r="CC10" s="122">
         <v>42066</v>
       </c>
     </row>
@@ -31636,16 +31608,16 @@
         <v/>
       </c>
       <c r="AE11" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP11" t="s">
         <v>180</v>
       </c>
       <c r="AQ11" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV11" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ11">
         <v>1</v>
@@ -31680,13 +31652,13 @@
       <c r="BV11">
         <v>55</v>
       </c>
-      <c r="BX11" s="130">
+      <c r="BX11" s="122">
         <v>42030</v>
       </c>
-      <c r="CB11" s="130">
+      <c r="CB11" s="122">
         <v>42029</v>
       </c>
-      <c r="CC11" s="130">
+      <c r="CC11" s="122">
         <v>42069</v>
       </c>
     </row>
@@ -31807,16 +31779,16 @@
         <v/>
       </c>
       <c r="AE12" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AP12" t="s">
         <v>180</v>
       </c>
       <c r="AQ12" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV12" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ12">
         <v>101</v>
@@ -31851,13 +31823,13 @@
       <c r="BV12">
         <v>1055</v>
       </c>
-      <c r="BX12" s="130">
+      <c r="BX12" s="122">
         <v>42033</v>
       </c>
-      <c r="CB12" s="130">
+      <c r="CB12" s="122">
         <v>42032</v>
       </c>
-      <c r="CC12" s="130">
+      <c r="CC12" s="122">
         <v>42072</v>
       </c>
     </row>
@@ -31978,16 +31950,16 @@
         <v/>
       </c>
       <c r="AE13" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP13" t="s">
         <v>180</v>
       </c>
       <c r="AQ13" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV13" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ13">
         <v>201</v>
@@ -32022,13 +31994,13 @@
       <c r="BV13">
         <v>2055</v>
       </c>
-      <c r="BX13" s="130">
+      <c r="BX13" s="122">
         <v>42036</v>
       </c>
-      <c r="CB13" s="130">
+      <c r="CB13" s="122">
         <v>42035</v>
       </c>
-      <c r="CC13" s="130">
+      <c r="CC13" s="122">
         <v>42075</v>
       </c>
     </row>
@@ -32149,16 +32121,16 @@
         <v/>
       </c>
       <c r="AE14" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP14" t="s">
         <v>180</v>
       </c>
       <c r="AQ14" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV14" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ14">
         <v>301</v>
@@ -32193,13 +32165,13 @@
       <c r="BV14">
         <v>3055</v>
       </c>
-      <c r="BX14" s="130">
+      <c r="BX14" s="122">
         <v>42039</v>
       </c>
-      <c r="CB14" s="130">
+      <c r="CB14" s="122">
         <v>42038</v>
       </c>
-      <c r="CC14" s="130">
+      <c r="CC14" s="122">
         <v>42078</v>
       </c>
     </row>
@@ -32320,16 +32292,16 @@
         <v/>
       </c>
       <c r="AE15" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP15" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ15" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV15" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ15">
         <v>401</v>
@@ -32364,13 +32336,13 @@
       <c r="BV15">
         <v>4055</v>
       </c>
-      <c r="BX15" s="130">
+      <c r="BX15" s="122">
         <v>42042</v>
       </c>
-      <c r="CB15" s="130">
+      <c r="CB15" s="122">
         <v>42041</v>
       </c>
-      <c r="CC15" s="130">
+      <c r="CC15" s="122">
         <v>42081</v>
       </c>
     </row>
@@ -32491,16 +32463,16 @@
         <v/>
       </c>
       <c r="AE16" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP16" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ16" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV16" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ16">
         <v>501</v>
@@ -32535,13 +32507,13 @@
       <c r="BV16">
         <v>5055</v>
       </c>
-      <c r="BX16" s="130">
+      <c r="BX16" s="122">
         <v>42045</v>
       </c>
-      <c r="CB16" s="130">
+      <c r="CB16" s="122">
         <v>42044</v>
       </c>
-      <c r="CC16" s="130">
+      <c r="CC16" s="122">
         <v>42084</v>
       </c>
     </row>
@@ -32662,16 +32634,16 @@
         <v/>
       </c>
       <c r="AE17" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP17" t="s">
         <v>180</v>
       </c>
       <c r="AQ17" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AV17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ17">
         <v>1</v>
@@ -32706,13 +32678,13 @@
       <c r="BV17">
         <v>55</v>
       </c>
-      <c r="BX17" s="130">
+      <c r="BX17" s="122">
         <v>42048</v>
       </c>
-      <c r="CB17" s="130">
+      <c r="CB17" s="122">
         <v>42047</v>
       </c>
-      <c r="CC17" s="130">
+      <c r="CC17" s="122">
         <v>42087</v>
       </c>
     </row>
@@ -32833,16 +32805,16 @@
         <v/>
       </c>
       <c r="AE18" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP18" t="s">
         <v>180</v>
       </c>
       <c r="AQ18" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV18" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ18">
         <v>101</v>
@@ -32877,13 +32849,13 @@
       <c r="BV18">
         <v>1055</v>
       </c>
-      <c r="BX18" s="130">
+      <c r="BX18" s="122">
         <v>42051</v>
       </c>
-      <c r="CB18" s="130">
+      <c r="CB18" s="122">
         <v>42050</v>
       </c>
-      <c r="CC18" s="130">
+      <c r="CC18" s="122">
         <v>42090</v>
       </c>
     </row>
@@ -33004,16 +32976,16 @@
         <v/>
       </c>
       <c r="AE19" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP19" t="s">
         <v>180</v>
       </c>
       <c r="AQ19" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AV19" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ19">
         <v>201</v>
@@ -33048,13 +33020,13 @@
       <c r="BV19">
         <v>2055</v>
       </c>
-      <c r="BX19" s="130">
+      <c r="BX19" s="122">
         <v>42054</v>
       </c>
-      <c r="CB19" s="130">
+      <c r="CB19" s="122">
         <v>42053</v>
       </c>
-      <c r="CC19" s="130">
+      <c r="CC19" s="122">
         <v>42093</v>
       </c>
     </row>
@@ -33175,16 +33147,16 @@
         <v/>
       </c>
       <c r="AE20" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP20" t="s">
         <v>180</v>
       </c>
       <c r="AQ20" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV20" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ20">
         <v>301</v>
@@ -33219,13 +33191,13 @@
       <c r="BV20">
         <v>3055</v>
       </c>
-      <c r="BX20" s="130">
+      <c r="BX20" s="122">
         <v>42057</v>
       </c>
-      <c r="CB20" s="130">
+      <c r="CB20" s="122">
         <v>42056</v>
       </c>
-      <c r="CC20" s="130">
+      <c r="CC20" s="122">
         <v>42096</v>
       </c>
     </row>
@@ -33346,16 +33318,16 @@
         <v/>
       </c>
       <c r="AE21" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP21" t="s">
         <v>180</v>
       </c>
       <c r="AQ21" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AV21" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ21">
         <v>1</v>
@@ -33390,13 +33362,13 @@
       <c r="BV21">
         <v>55</v>
       </c>
-      <c r="BX21" s="130">
+      <c r="BX21" s="122">
         <v>42060</v>
       </c>
-      <c r="CB21" s="130">
+      <c r="CB21" s="122">
         <v>42059</v>
       </c>
-      <c r="CC21" s="130">
+      <c r="CC21" s="122">
         <v>42099</v>
       </c>
     </row>
@@ -33517,13 +33489,13 @@
         <v/>
       </c>
       <c r="AE22" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AP22" t="s">
         <v>180</v>
       </c>
       <c r="AV22" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ22">
         <v>101</v>
@@ -33558,13 +33530,13 @@
       <c r="BV22">
         <v>1055</v>
       </c>
-      <c r="BX22" s="130">
+      <c r="BX22" s="122">
         <v>42063</v>
       </c>
-      <c r="CB22" s="130">
+      <c r="CB22" s="122">
         <v>42062</v>
       </c>
-      <c r="CC22" s="130">
+      <c r="CC22" s="122">
         <v>42102</v>
       </c>
     </row>
@@ -33685,16 +33657,16 @@
         <v/>
       </c>
       <c r="AE23" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP23" t="s">
         <v>292</v>
       </c>
-      <c r="AP23" t="s">
-        <v>301</v>
-      </c>
       <c r="AQ23" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV23" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ23">
         <v>201</v>
@@ -33729,13 +33701,13 @@
       <c r="BV23">
         <v>2055</v>
       </c>
-      <c r="BX23" s="130">
+      <c r="BX23" s="122">
         <v>42066</v>
       </c>
-      <c r="CB23" s="130">
+      <c r="CB23" s="122">
         <v>42065</v>
       </c>
-      <c r="CC23" s="130">
+      <c r="CC23" s="122">
         <v>42105</v>
       </c>
     </row>
@@ -33856,16 +33828,16 @@
         <v/>
       </c>
       <c r="AE24" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP24" t="s">
         <v>292</v>
       </c>
-      <c r="AP24" t="s">
-        <v>301</v>
-      </c>
       <c r="AQ24" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV24" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ24">
         <v>301</v>
@@ -33900,13 +33872,13 @@
       <c r="BV24">
         <v>3055</v>
       </c>
-      <c r="BX24" s="130">
+      <c r="BX24" s="122">
         <v>42069</v>
       </c>
-      <c r="CB24" s="130">
+      <c r="CB24" s="122">
         <v>42068</v>
       </c>
-      <c r="CC24" s="130">
+      <c r="CC24" s="122">
         <v>42108</v>
       </c>
     </row>
@@ -34027,16 +33999,16 @@
         <v/>
       </c>
       <c r="AE25" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s">
         <v>180</v>
       </c>
       <c r="AQ25" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV25" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ25">
         <v>401</v>
@@ -34071,13 +34043,13 @@
       <c r="BV25">
         <v>4055</v>
       </c>
-      <c r="BX25" s="130">
+      <c r="BX25" s="122">
         <v>42072</v>
       </c>
-      <c r="CB25" s="130">
+      <c r="CB25" s="122">
         <v>42071</v>
       </c>
-      <c r="CC25" s="130">
+      <c r="CC25" s="122">
         <v>42111</v>
       </c>
     </row>
@@ -34198,16 +34170,16 @@
         <v/>
       </c>
       <c r="AE26" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AP26" t="s">
         <v>180</v>
       </c>
       <c r="AQ26" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AV26" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ26">
         <v>501</v>
@@ -34242,13 +34214,13 @@
       <c r="BV26">
         <v>5055</v>
       </c>
-      <c r="BX26" s="130">
+      <c r="BX26" s="122">
         <v>42075</v>
       </c>
-      <c r="CB26" s="130">
+      <c r="CB26" s="122">
         <v>42074</v>
       </c>
-      <c r="CC26" s="130">
+      <c r="CC26" s="122">
         <v>42114</v>
       </c>
     </row>
@@ -34369,16 +34341,16 @@
         <v/>
       </c>
       <c r="AE27" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AP27" t="s">
         <v>180</v>
       </c>
       <c r="AQ27" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV27" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ27">
         <v>601</v>
@@ -34413,13 +34385,13 @@
       <c r="BV27">
         <v>6055</v>
       </c>
-      <c r="BX27" s="130">
+      <c r="BX27" s="122">
         <v>42078</v>
       </c>
-      <c r="CB27" s="130">
+      <c r="CB27" s="122">
         <v>42077</v>
       </c>
-      <c r="CC27" s="130">
+      <c r="CC27" s="122">
         <v>42117</v>
       </c>
     </row>
@@ -34540,16 +34512,16 @@
         <v/>
       </c>
       <c r="AE28" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AP28" t="s">
         <v>180</v>
       </c>
       <c r="AQ28" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV28" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ28">
         <v>1</v>
@@ -34584,13 +34556,13 @@
       <c r="BV28">
         <v>55</v>
       </c>
-      <c r="BX28" s="130">
+      <c r="BX28" s="122">
         <v>42081</v>
       </c>
-      <c r="CB28" s="130">
+      <c r="CB28" s="122">
         <v>42080</v>
       </c>
-      <c r="CC28" s="130">
+      <c r="CC28" s="122">
         <v>42120</v>
       </c>
     </row>
@@ -34711,16 +34683,16 @@
         <v/>
       </c>
       <c r="AE29" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AP29" t="s">
         <v>180</v>
       </c>
       <c r="AQ29" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV29" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ29">
         <v>101</v>
@@ -34755,13 +34727,13 @@
       <c r="BV29">
         <v>1055</v>
       </c>
-      <c r="BX29" s="130">
+      <c r="BX29" s="122">
         <v>42084</v>
       </c>
-      <c r="CB29" s="130">
+      <c r="CB29" s="122">
         <v>42083</v>
       </c>
-      <c r="CC29" s="130">
+      <c r="CC29" s="122">
         <v>42123</v>
       </c>
     </row>
@@ -34882,16 +34854,16 @@
         <v/>
       </c>
       <c r="AE30" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AP30" t="s">
         <v>180</v>
       </c>
       <c r="AQ30" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV30" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="BJ30">
         <v>201</v>
@@ -34926,13 +34898,13 @@
       <c r="BV30">
         <v>2055</v>
       </c>
-      <c r="BX30" s="130">
+      <c r="BX30" s="122">
         <v>42087</v>
       </c>
-      <c r="CB30" s="130">
+      <c r="CB30" s="122">
         <v>42086</v>
       </c>
-      <c r="CC30" s="130">
+      <c r="CC30" s="122">
         <v>42126</v>
       </c>
     </row>
@@ -35053,16 +35025,16 @@
         <v/>
       </c>
       <c r="AE31" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP31" t="s">
         <v>292</v>
       </c>
-      <c r="AP31" t="s">
-        <v>301</v>
-      </c>
       <c r="AQ31" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV31" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ31">
         <v>301</v>
@@ -35097,13 +35069,13 @@
       <c r="BV31">
         <v>3055</v>
       </c>
-      <c r="BX31" s="130">
+      <c r="BX31" s="122">
         <v>42090</v>
       </c>
-      <c r="CB31" s="130">
+      <c r="CB31" s="122">
         <v>42089</v>
       </c>
-      <c r="CC31" s="130">
+      <c r="CC31" s="122">
         <v>42129</v>
       </c>
     </row>
@@ -35224,13 +35196,13 @@
         <v/>
       </c>
       <c r="AE32" t="s">
+        <v>283</v>
+      </c>
+      <c r="AP32" t="s">
         <v>292</v>
       </c>
-      <c r="AP32" t="s">
-        <v>301</v>
-      </c>
       <c r="AV32" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ32">
         <v>401</v>
@@ -35265,13 +35237,13 @@
       <c r="BV32">
         <v>4055</v>
       </c>
-      <c r="BX32" s="130">
+      <c r="BX32" s="122">
         <v>42093</v>
       </c>
-      <c r="CB32" s="130">
+      <c r="CB32" s="122">
         <v>42092</v>
       </c>
-      <c r="CC32" s="130">
+      <c r="CC32" s="122">
         <v>42132</v>
       </c>
     </row>
@@ -35392,13 +35364,13 @@
         <v/>
       </c>
       <c r="AE33" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>292</v>
+      </c>
+      <c r="AV33" t="s">
         <v>293</v>
-      </c>
-      <c r="AP33" t="s">
-        <v>301</v>
-      </c>
-      <c r="AV33" t="s">
-        <v>302</v>
       </c>
       <c r="BJ33">
         <v>501</v>
@@ -35433,13 +35405,13 @@
       <c r="BV33">
         <v>5055</v>
       </c>
-      <c r="BX33" s="130">
+      <c r="BX33" s="122">
         <v>42096</v>
       </c>
-      <c r="CB33" s="130">
+      <c r="CB33" s="122">
         <v>42095</v>
       </c>
-      <c r="CC33" s="130">
+      <c r="CC33" s="122">
         <v>42135</v>
       </c>
     </row>
@@ -35560,16 +35532,16 @@
         <v/>
       </c>
       <c r="AE34" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AP34" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ34" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV34" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ34">
         <v>601</v>
@@ -35604,13 +35576,13 @@
       <c r="BV34">
         <v>6055</v>
       </c>
-      <c r="BX34" s="130">
+      <c r="BX34" s="122">
         <v>42099</v>
       </c>
-      <c r="CB34" s="130">
+      <c r="CB34" s="122">
         <v>42098</v>
       </c>
-      <c r="CC34" s="130">
+      <c r="CC34" s="122">
         <v>42138</v>
       </c>
     </row>
@@ -35731,13 +35703,13 @@
         <v/>
       </c>
       <c r="AE35" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP35" t="s">
+        <v>292</v>
+      </c>
+      <c r="AV35" t="s">
         <v>293</v>
-      </c>
-      <c r="AP35" t="s">
-        <v>301</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>302</v>
       </c>
       <c r="BJ35">
         <v>1</v>
@@ -35772,13 +35744,13 @@
       <c r="BV35">
         <v>55</v>
       </c>
-      <c r="BX35" s="130">
+      <c r="BX35" s="122">
         <v>42102</v>
       </c>
-      <c r="CB35" s="130">
+      <c r="CB35" s="122">
         <v>42101</v>
       </c>
-      <c r="CC35" s="130">
+      <c r="CC35" s="122">
         <v>42141</v>
       </c>
     </row>
@@ -35899,13 +35871,13 @@
         <v/>
       </c>
       <c r="AE36" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP36" t="s">
+        <v>292</v>
+      </c>
+      <c r="AV36" t="s">
         <v>293</v>
-      </c>
-      <c r="AP36" t="s">
-        <v>301</v>
-      </c>
-      <c r="AV36" t="s">
-        <v>302</v>
       </c>
       <c r="BJ36">
         <v>101</v>
@@ -35940,13 +35912,13 @@
       <c r="BV36">
         <v>1055</v>
       </c>
-      <c r="BX36" s="130">
+      <c r="BX36" s="122">
         <v>42105</v>
       </c>
-      <c r="CB36" s="130">
+      <c r="CB36" s="122">
         <v>42104</v>
       </c>
-      <c r="CC36" s="130">
+      <c r="CC36" s="122">
         <v>42144</v>
       </c>
     </row>
@@ -36067,16 +36039,16 @@
         <v/>
       </c>
       <c r="AE37" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP37" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>300</v>
+      </c>
+      <c r="AV37" t="s">
         <v>293</v>
-      </c>
-      <c r="AP37" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ37" t="s">
-        <v>309</v>
-      </c>
-      <c r="AV37" t="s">
-        <v>302</v>
       </c>
       <c r="BJ37">
         <v>201</v>
@@ -36111,13 +36083,13 @@
       <c r="BV37">
         <v>2055</v>
       </c>
-      <c r="BX37" s="130">
+      <c r="BX37" s="122">
         <v>42108</v>
       </c>
-      <c r="CB37" s="130">
+      <c r="CB37" s="122">
         <v>42107</v>
       </c>
-      <c r="CC37" s="130">
+      <c r="CC37" s="122">
         <v>42147</v>
       </c>
     </row>
@@ -36238,16 +36210,16 @@
         <v/>
       </c>
       <c r="AE38" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AP38" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ38" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV38" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="BJ38">
         <v>301</v>
@@ -36282,13 +36254,13 @@
       <c r="BV38">
         <v>3055</v>
       </c>
-      <c r="BX38" s="130">
+      <c r="BX38" s="122">
         <v>42111</v>
       </c>
-      <c r="CB38" s="130">
+      <c r="CB38" s="122">
         <v>42110</v>
       </c>
-      <c r="CC38" s="130">
+      <c r="CC38" s="122">
         <v>42150</v>
       </c>
     </row>
@@ -36409,16 +36381,16 @@
         <v/>
       </c>
       <c r="AE39" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP39" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>303</v>
+      </c>
+      <c r="AV39" t="s">
         <v>293</v>
-      </c>
-      <c r="AP39" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ39" t="s">
-        <v>312</v>
-      </c>
-      <c r="AV39" t="s">
-        <v>302</v>
       </c>
       <c r="BJ39">
         <v>401</v>
@@ -36453,13 +36425,13 @@
       <c r="BV39">
         <v>4055</v>
       </c>
-      <c r="BX39" s="130">
+      <c r="BX39" s="122">
         <v>42114</v>
       </c>
-      <c r="CB39" s="130">
+      <c r="CB39" s="122">
         <v>42113</v>
       </c>
-      <c r="CC39" s="130">
+      <c r="CC39" s="122">
         <v>42153</v>
       </c>
     </row>
@@ -36580,16 +36552,16 @@
         <v/>
       </c>
       <c r="AE40" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP40" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>298</v>
+      </c>
+      <c r="AV40" t="s">
         <v>293</v>
-      </c>
-      <c r="AP40" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ40" t="s">
-        <v>307</v>
-      </c>
-      <c r="AV40" t="s">
-        <v>302</v>
       </c>
       <c r="BJ40">
         <v>501</v>
@@ -36624,13 +36596,13 @@
       <c r="BV40">
         <v>5055</v>
       </c>
-      <c r="BX40" s="130">
+      <c r="BX40" s="122">
         <v>42117</v>
       </c>
-      <c r="CB40" s="130">
+      <c r="CB40" s="122">
         <v>42116</v>
       </c>
-      <c r="CC40" s="130">
+      <c r="CC40" s="122">
         <v>42156</v>
       </c>
     </row>
@@ -36751,16 +36723,16 @@
         <v/>
       </c>
       <c r="AE41" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP41" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ41" t="s">
+        <v>298</v>
+      </c>
+      <c r="AV41" t="s">
         <v>293</v>
-      </c>
-      <c r="AP41" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ41" t="s">
-        <v>307</v>
-      </c>
-      <c r="AV41" t="s">
-        <v>302</v>
       </c>
       <c r="BJ41">
         <v>601</v>
@@ -36795,13 +36767,13 @@
       <c r="BV41">
         <v>6055</v>
       </c>
-      <c r="BX41" s="130">
+      <c r="BX41" s="122">
         <v>42120</v>
       </c>
-      <c r="CB41" s="130">
+      <c r="CB41" s="122">
         <v>42119</v>
       </c>
-      <c r="CC41" s="130">
+      <c r="CC41" s="122">
         <v>42159</v>
       </c>
     </row>
@@ -36922,16 +36894,16 @@
         <v/>
       </c>
       <c r="AE42" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AP42" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ42" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV42" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ42">
         <v>1</v>
@@ -36966,13 +36938,13 @@
       <c r="BV42">
         <v>55</v>
       </c>
-      <c r="BX42" s="130">
+      <c r="BX42" s="122">
         <v>42123</v>
       </c>
-      <c r="CB42" s="130">
+      <c r="CB42" s="122">
         <v>42122</v>
       </c>
-      <c r="CC42" s="130">
+      <c r="CC42" s="122">
         <v>42162</v>
       </c>
     </row>
@@ -37093,16 +37065,16 @@
         <v/>
       </c>
       <c r="AE43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ43" t="s">
+        <v>301</v>
+      </c>
+      <c r="AV43" t="s">
         <v>294</v>
-      </c>
-      <c r="AP43" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ43" t="s">
-        <v>310</v>
-      </c>
-      <c r="AV43" t="s">
-        <v>303</v>
       </c>
       <c r="BJ43">
         <v>101</v>
@@ -37137,13 +37109,13 @@
       <c r="BV43">
         <v>1055</v>
       </c>
-      <c r="BX43" s="130">
+      <c r="BX43" s="122">
         <v>42126</v>
       </c>
-      <c r="CB43" s="130">
+      <c r="CB43" s="122">
         <v>42125</v>
       </c>
-      <c r="CC43" s="130">
+      <c r="CC43" s="122">
         <v>42165</v>
       </c>
     </row>
@@ -37264,16 +37236,16 @@
         <v/>
       </c>
       <c r="AE44" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP44" t="s">
         <v>180</v>
       </c>
       <c r="AQ44" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AV44" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ44">
         <v>201</v>
@@ -37308,13 +37280,13 @@
       <c r="BV44">
         <v>2055</v>
       </c>
-      <c r="BX44" s="130">
+      <c r="BX44" s="122">
         <v>42129</v>
       </c>
-      <c r="CB44" s="130">
+      <c r="CB44" s="122">
         <v>42128</v>
       </c>
-      <c r="CC44" s="130">
+      <c r="CC44" s="122">
         <v>42168</v>
       </c>
     </row>
@@ -37435,16 +37407,16 @@
         <v/>
       </c>
       <c r="AE45" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP45" t="s">
         <v>180</v>
       </c>
       <c r="AQ45" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV45" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="BJ45">
         <v>301</v>
@@ -37479,13 +37451,13 @@
       <c r="BV45">
         <v>3055</v>
       </c>
-      <c r="BX45" s="130">
+      <c r="BX45" s="122">
         <v>42132</v>
       </c>
-      <c r="CB45" s="130">
+      <c r="CB45" s="122">
         <v>42131</v>
       </c>
-      <c r="CC45" s="130">
+      <c r="CC45" s="122">
         <v>42171</v>
       </c>
     </row>
@@ -37606,16 +37578,16 @@
         <v/>
       </c>
       <c r="AE46" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP46" t="s">
         <v>180</v>
       </c>
       <c r="AQ46" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV46" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ46">
         <v>401</v>
@@ -37650,13 +37622,13 @@
       <c r="BV46">
         <v>4055</v>
       </c>
-      <c r="BX46" s="130">
+      <c r="BX46" s="122">
         <v>42135</v>
       </c>
-      <c r="CB46" s="130">
+      <c r="CB46" s="122">
         <v>42134</v>
       </c>
-      <c r="CC46" s="130">
+      <c r="CC46" s="122">
         <v>42174</v>
       </c>
     </row>
@@ -37777,16 +37749,16 @@
         <v/>
       </c>
       <c r="AE47" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP47" t="s">
         <v>180</v>
       </c>
       <c r="AQ47" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV47" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ47">
         <v>501</v>
@@ -37821,13 +37793,13 @@
       <c r="BV47">
         <v>5055</v>
       </c>
-      <c r="BX47" s="130">
+      <c r="BX47" s="122">
         <v>42138</v>
       </c>
-      <c r="CB47" s="130">
+      <c r="CB47" s="122">
         <v>42137</v>
       </c>
-      <c r="CC47" s="130">
+      <c r="CC47" s="122">
         <v>42177</v>
       </c>
     </row>
@@ -37948,16 +37920,16 @@
         <v/>
       </c>
       <c r="AE48" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP48" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ48" t="s">
         <v>301</v>
       </c>
-      <c r="AQ48" t="s">
-        <v>310</v>
-      </c>
       <c r="AV48" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ48">
         <v>601</v>
@@ -37992,13 +37964,13 @@
       <c r="BV48">
         <v>6055</v>
       </c>
-      <c r="BX48" s="130">
+      <c r="BX48" s="122">
         <v>42141</v>
       </c>
-      <c r="CB48" s="130">
+      <c r="CB48" s="122">
         <v>42140</v>
       </c>
-      <c r="CC48" s="130">
+      <c r="CC48" s="122">
         <v>42180</v>
       </c>
     </row>
@@ -38119,16 +38091,16 @@
         <v/>
       </c>
       <c r="AE49" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP49" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ49" t="s">
         <v>301</v>
       </c>
-      <c r="AQ49" t="s">
-        <v>310</v>
-      </c>
       <c r="AV49" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ49">
         <v>1</v>
@@ -38163,13 +38135,13 @@
       <c r="BV49">
         <v>55</v>
       </c>
-      <c r="BX49" s="130">
+      <c r="BX49" s="122">
         <v>42144</v>
       </c>
-      <c r="CB49" s="130">
+      <c r="CB49" s="122">
         <v>42143</v>
       </c>
-      <c r="CC49" s="130">
+      <c r="CC49" s="122">
         <v>42183</v>
       </c>
     </row>
@@ -38290,16 +38262,16 @@
         <v/>
       </c>
       <c r="AE50" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP50" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ50" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV50" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ50">
         <v>101</v>
@@ -38334,13 +38306,13 @@
       <c r="BV50">
         <v>1055</v>
       </c>
-      <c r="BX50" s="130">
+      <c r="BX50" s="122">
         <v>42147</v>
       </c>
-      <c r="CB50" s="130">
+      <c r="CB50" s="122">
         <v>42146</v>
       </c>
-      <c r="CC50" s="130">
+      <c r="CC50" s="122">
         <v>42186</v>
       </c>
     </row>
@@ -38461,16 +38433,16 @@
         <v/>
       </c>
       <c r="AE51" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="AP51" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ51" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV51" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ51">
         <v>201</v>
@@ -38505,13 +38477,13 @@
       <c r="BV51">
         <v>2055</v>
       </c>
-      <c r="BX51" s="130">
+      <c r="BX51" s="122">
         <v>42150</v>
       </c>
-      <c r="CB51" s="130">
+      <c r="CB51" s="122">
         <v>42149</v>
       </c>
-      <c r="CC51" s="130">
+      <c r="CC51" s="122">
         <v>42189</v>
       </c>
     </row>
@@ -38632,16 +38604,16 @@
         <v/>
       </c>
       <c r="AE52" t="s">
+        <v>285</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ52" t="s">
+        <v>300</v>
+      </c>
+      <c r="AV52" t="s">
         <v>294</v>
-      </c>
-      <c r="AP52" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ52" t="s">
-        <v>309</v>
-      </c>
-      <c r="AV52" t="s">
-        <v>303</v>
       </c>
       <c r="BJ52">
         <v>301</v>
@@ -38676,13 +38648,13 @@
       <c r="BV52">
         <v>3055</v>
       </c>
-      <c r="BX52" s="130">
+      <c r="BX52" s="122">
         <v>42153</v>
       </c>
-      <c r="CB52" s="130">
+      <c r="CB52" s="122">
         <v>42152</v>
       </c>
-      <c r="CC52" s="130">
+      <c r="CC52" s="122">
         <v>42192</v>
       </c>
     </row>
@@ -38803,16 +38775,16 @@
         <v/>
       </c>
       <c r="AE53" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP53" t="s">
         <v>180</v>
       </c>
       <c r="AQ53" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AV53" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="BJ53">
         <v>401</v>
@@ -38847,13 +38819,13 @@
       <c r="BV53">
         <v>4055</v>
       </c>
-      <c r="BX53" s="130">
+      <c r="BX53" s="122">
         <v>42156</v>
       </c>
-      <c r="CB53" s="130">
+      <c r="CB53" s="122">
         <v>42155</v>
       </c>
-      <c r="CC53" s="130">
+      <c r="CC53" s="122">
         <v>42195</v>
       </c>
     </row>
@@ -38974,13 +38946,13 @@
         <v/>
       </c>
       <c r="AE54" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP54" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AV54" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="BJ54">
         <v>501</v>
@@ -39015,13 +38987,13 @@
       <c r="BV54">
         <v>5055</v>
       </c>
-      <c r="BX54" s="130">
+      <c r="BX54" s="122">
         <v>42159</v>
       </c>
-      <c r="CB54" s="130">
+      <c r="CB54" s="122">
         <v>42158</v>
       </c>
-      <c r="CC54" s="130">
+      <c r="CC54" s="122">
         <v>42198</v>
       </c>
     </row>
@@ -39142,13 +39114,13 @@
         <v/>
       </c>
       <c r="AE55" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP55" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AV55" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ55">
         <v>1</v>
@@ -39183,13 +39155,13 @@
       <c r="BV55">
         <v>55</v>
       </c>
-      <c r="BX55" s="130">
+      <c r="BX55" s="122">
         <v>42162</v>
       </c>
-      <c r="CB55" s="130">
+      <c r="CB55" s="122">
         <v>42161</v>
       </c>
-      <c r="CC55" s="130">
+      <c r="CC55" s="122">
         <v>42201</v>
       </c>
     </row>
@@ -39310,13 +39282,13 @@
         <v/>
       </c>
       <c r="AE56" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP56" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AV56" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ56">
         <v>101</v>
@@ -39351,13 +39323,13 @@
       <c r="BV56">
         <v>1055</v>
       </c>
-      <c r="BX56" s="130">
+      <c r="BX56" s="122">
         <v>42165</v>
       </c>
-      <c r="CB56" s="130">
+      <c r="CB56" s="122">
         <v>42164</v>
       </c>
-      <c r="CC56" s="130">
+      <c r="CC56" s="122">
         <v>42204</v>
       </c>
     </row>
@@ -39478,13 +39450,13 @@
         <v/>
       </c>
       <c r="AE57" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP57" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AV57" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ57">
         <v>201</v>
@@ -39519,13 +39491,13 @@
       <c r="BV57">
         <v>2055</v>
       </c>
-      <c r="BX57" s="130">
+      <c r="BX57" s="122">
         <v>42168</v>
       </c>
-      <c r="CB57" s="130">
+      <c r="CB57" s="122">
         <v>42167</v>
       </c>
-      <c r="CC57" s="130">
+      <c r="CC57" s="122">
         <v>42207</v>
       </c>
     </row>
@@ -39646,16 +39618,16 @@
         <v/>
       </c>
       <c r="AE58" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP58" t="s">
         <v>180</v>
       </c>
       <c r="AQ58" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AV58" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="BJ58">
         <v>301</v>
@@ -39690,13 +39662,13 @@
       <c r="BV58">
         <v>3055</v>
       </c>
-      <c r="BX58" s="130">
+      <c r="BX58" s="122">
         <v>42171</v>
       </c>
-      <c r="CB58" s="130">
+      <c r="CB58" s="122">
         <v>42170</v>
       </c>
-      <c r="CC58" s="130">
+      <c r="CC58" s="122">
         <v>42210</v>
       </c>
     </row>
@@ -39817,16 +39789,16 @@
         <v/>
       </c>
       <c r="AE59" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP59" t="s">
         <v>180</v>
       </c>
       <c r="AQ59" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV59" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ59">
         <v>401</v>
@@ -39861,13 +39833,13 @@
       <c r="BV59">
         <v>4055</v>
       </c>
-      <c r="BX59" s="130">
+      <c r="BX59" s="122">
         <v>42174</v>
       </c>
-      <c r="CB59" s="130">
+      <c r="CB59" s="122">
         <v>42173</v>
       </c>
-      <c r="CC59" s="130">
+      <c r="CC59" s="122">
         <v>42213</v>
       </c>
     </row>
@@ -39988,16 +39960,16 @@
         <v/>
       </c>
       <c r="AE60" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP60" t="s">
         <v>180</v>
       </c>
       <c r="AQ60" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV60" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="BJ60">
         <v>501</v>
@@ -40032,13 +40004,13 @@
       <c r="BV60">
         <v>5055</v>
       </c>
-      <c r="BX60" s="130">
+      <c r="BX60" s="122">
         <v>42177</v>
       </c>
-      <c r="CB60" s="130">
+      <c r="CB60" s="122">
         <v>42176</v>
       </c>
-      <c r="CC60" s="130">
+      <c r="CC60" s="122">
         <v>42216</v>
       </c>
     </row>
@@ -40159,13 +40131,13 @@
         <v/>
       </c>
       <c r="AE61" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP61" t="s">
         <v>180</v>
       </c>
       <c r="AV61" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ61">
         <v>601</v>
@@ -40200,13 +40172,13 @@
       <c r="BV61">
         <v>6055</v>
       </c>
-      <c r="BX61" s="130">
+      <c r="BX61" s="122">
         <v>42180</v>
       </c>
-      <c r="CB61" s="130">
+      <c r="CB61" s="122">
         <v>42179</v>
       </c>
-      <c r="CC61" s="130">
+      <c r="CC61" s="122">
         <v>42219</v>
       </c>
     </row>
@@ -40327,16 +40299,16 @@
         <v/>
       </c>
       <c r="AE62" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AP62" t="s">
         <v>180</v>
       </c>
       <c r="AQ62" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV62" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ62">
         <v>1</v>
@@ -40371,13 +40343,13 @@
       <c r="BV62">
         <v>55</v>
       </c>
-      <c r="BX62" s="130">
+      <c r="BX62" s="122">
         <v>42183</v>
       </c>
-      <c r="CB62" s="130">
+      <c r="CB62" s="122">
         <v>42182</v>
       </c>
-      <c r="CC62" s="130">
+      <c r="CC62" s="122">
         <v>42222</v>
       </c>
     </row>
@@ -40498,16 +40470,16 @@
         <v/>
       </c>
       <c r="AE63" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP63" t="s">
         <v>180</v>
       </c>
       <c r="AQ63" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV63" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ63">
         <v>101</v>
@@ -40542,13 +40514,13 @@
       <c r="BV63">
         <v>1055</v>
       </c>
-      <c r="BX63" s="130">
+      <c r="BX63" s="122">
         <v>42186</v>
       </c>
-      <c r="CB63" s="130">
+      <c r="CB63" s="122">
         <v>42185</v>
       </c>
-      <c r="CC63" s="130">
+      <c r="CC63" s="122">
         <v>42225</v>
       </c>
     </row>
@@ -40669,16 +40641,16 @@
         <v/>
       </c>
       <c r="AE64" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP64" t="s">
         <v>180</v>
       </c>
       <c r="AQ64" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV64" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ64">
         <v>201</v>
@@ -40713,13 +40685,13 @@
       <c r="BV64">
         <v>2055</v>
       </c>
-      <c r="BX64" s="130">
+      <c r="BX64" s="122">
         <v>42189</v>
       </c>
-      <c r="CB64" s="130">
+      <c r="CB64" s="122">
         <v>42188</v>
       </c>
-      <c r="CC64" s="130">
+      <c r="CC64" s="122">
         <v>42228</v>
       </c>
     </row>
@@ -40840,16 +40812,16 @@
         <v/>
       </c>
       <c r="AE65" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP65" t="s">
         <v>180</v>
       </c>
       <c r="AQ65" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV65" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ65">
         <v>301</v>
@@ -40884,13 +40856,13 @@
       <c r="BV65">
         <v>3055</v>
       </c>
-      <c r="BX65" s="130">
+      <c r="BX65" s="122">
         <v>42192</v>
       </c>
-      <c r="CB65" s="130">
+      <c r="CB65" s="122">
         <v>42191</v>
       </c>
-      <c r="CC65" s="130">
+      <c r="CC65" s="122">
         <v>42231</v>
       </c>
     </row>
@@ -41011,16 +40983,16 @@
         <v/>
       </c>
       <c r="AE66" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP66" t="s">
         <v>180</v>
       </c>
       <c r="AQ66" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV66" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ66">
         <v>401</v>
@@ -41055,13 +41027,13 @@
       <c r="BV66">
         <v>4055</v>
       </c>
-      <c r="BX66" s="130">
+      <c r="BX66" s="122">
         <v>42195</v>
       </c>
-      <c r="CB66" s="130">
+      <c r="CB66" s="122">
         <v>42194</v>
       </c>
-      <c r="CC66" s="130">
+      <c r="CC66" s="122">
         <v>42234</v>
       </c>
     </row>
@@ -41182,16 +41154,16 @@
         <v/>
       </c>
       <c r="AE67" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP67" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ67" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AV67" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ67">
         <v>501</v>
@@ -41226,13 +41198,13 @@
       <c r="BV67">
         <v>5055</v>
       </c>
-      <c r="BX67" s="130">
+      <c r="BX67" s="122">
         <v>42198</v>
       </c>
-      <c r="CB67" s="130">
+      <c r="CB67" s="122">
         <v>42197</v>
       </c>
-      <c r="CC67" s="130">
+      <c r="CC67" s="122">
         <v>42237</v>
       </c>
     </row>
@@ -41353,16 +41325,16 @@
         <v/>
       </c>
       <c r="AE68" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP68" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ68" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV68" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ68">
         <v>601</v>
@@ -41397,13 +41369,13 @@
       <c r="BV68">
         <v>6055</v>
       </c>
-      <c r="BX68" s="130">
+      <c r="BX68" s="122">
         <v>42201</v>
       </c>
-      <c r="CB68" s="130">
+      <c r="CB68" s="122">
         <v>42200</v>
       </c>
-      <c r="CC68" s="130">
+      <c r="CC68" s="122">
         <v>42240</v>
       </c>
     </row>
@@ -41524,16 +41496,16 @@
         <v/>
       </c>
       <c r="AE69" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP69" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ69" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV69" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="BJ69">
         <v>1</v>
@@ -41568,13 +41540,13 @@
       <c r="BV69">
         <v>55</v>
       </c>
-      <c r="BX69" s="130">
+      <c r="BX69" s="122">
         <v>42204</v>
       </c>
-      <c r="CB69" s="130">
+      <c r="CB69" s="122">
         <v>42203</v>
       </c>
-      <c r="CC69" s="130">
+      <c r="CC69" s="122">
         <v>42243</v>
       </c>
     </row>
@@ -41695,16 +41667,16 @@
         <v/>
       </c>
       <c r="AE70" t="s">
+        <v>287</v>
+      </c>
+      <c r="AP70" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ70" t="s">
+        <v>300</v>
+      </c>
+      <c r="AV70" t="s">
         <v>296</v>
-      </c>
-      <c r="AP70" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ70" t="s">
-        <v>309</v>
-      </c>
-      <c r="AV70" t="s">
-        <v>305</v>
       </c>
       <c r="BJ70">
         <v>101</v>
@@ -41739,13 +41711,13 @@
       <c r="BV70">
         <v>1055</v>
       </c>
-      <c r="BX70" s="130">
+      <c r="BX70" s="122">
         <v>42207</v>
       </c>
-      <c r="CB70" s="130">
+      <c r="CB70" s="122">
         <v>42206</v>
       </c>
-      <c r="CC70" s="130">
+      <c r="CC70" s="122">
         <v>42246</v>
       </c>
     </row>
@@ -41866,16 +41838,16 @@
         <v/>
       </c>
       <c r="AE71" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP71" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ71" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV71" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ71">
         <v>201</v>
@@ -41910,13 +41882,13 @@
       <c r="BV71">
         <v>2055</v>
       </c>
-      <c r="BX71" s="130">
+      <c r="BX71" s="122">
         <v>42210</v>
       </c>
-      <c r="CB71" s="130">
+      <c r="CB71" s="122">
         <v>42209</v>
       </c>
-      <c r="CC71" s="130">
+      <c r="CC71" s="122">
         <v>42249</v>
       </c>
     </row>
@@ -42037,16 +42009,16 @@
         <v/>
       </c>
       <c r="AE72" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="AP72" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ72" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AV72" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ72">
         <v>301</v>
@@ -42081,13 +42053,13 @@
       <c r="BV72">
         <v>3055</v>
       </c>
-      <c r="BX72" s="130">
+      <c r="BX72" s="122">
         <v>42213</v>
       </c>
-      <c r="CB72" s="130">
+      <c r="CB72" s="122">
         <v>42212</v>
       </c>
-      <c r="CC72" s="130">
+      <c r="CC72" s="122">
         <v>42252</v>
       </c>
     </row>
@@ -42208,16 +42180,16 @@
         <v/>
       </c>
       <c r="AE73" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP73" t="s">
         <v>180</v>
       </c>
       <c r="AQ73" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV73" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ73">
         <v>401</v>
@@ -42252,13 +42224,13 @@
       <c r="BV73">
         <v>4055</v>
       </c>
-      <c r="BX73" s="130">
+      <c r="BX73" s="122">
         <v>42216</v>
       </c>
-      <c r="CB73" s="130">
+      <c r="CB73" s="122">
         <v>42215</v>
       </c>
-      <c r="CC73" s="130">
+      <c r="CC73" s="122">
         <v>42255</v>
       </c>
     </row>
@@ -42379,16 +42351,16 @@
         <v/>
       </c>
       <c r="AE74" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP74" t="s">
         <v>180</v>
       </c>
       <c r="AQ74" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV74" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ74">
         <v>501</v>
@@ -42423,13 +42395,13 @@
       <c r="BV74">
         <v>5055</v>
       </c>
-      <c r="BX74" s="130">
+      <c r="BX74" s="122">
         <v>42219</v>
       </c>
-      <c r="CB74" s="130">
+      <c r="CB74" s="122">
         <v>42218</v>
       </c>
-      <c r="CC74" s="130">
+      <c r="CC74" s="122">
         <v>42258</v>
       </c>
     </row>
@@ -42550,16 +42522,16 @@
         <v/>
       </c>
       <c r="AE75" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP75" t="s">
         <v>180</v>
       </c>
       <c r="AQ75" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV75" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="BJ75">
         <v>601</v>
@@ -42594,13 +42566,13 @@
       <c r="BV75">
         <v>6055</v>
       </c>
-      <c r="BX75" s="130">
+      <c r="BX75" s="122">
         <v>42222</v>
       </c>
-      <c r="CB75" s="130">
+      <c r="CB75" s="122">
         <v>42221</v>
       </c>
-      <c r="CC75" s="130">
+      <c r="CC75" s="122">
         <v>42261</v>
       </c>
     </row>
@@ -42721,16 +42693,16 @@
         <v/>
       </c>
       <c r="AE76" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP76" t="s">
         <v>180</v>
       </c>
       <c r="AQ76" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AV76" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ76">
         <v>1</v>
@@ -42765,13 +42737,13 @@
       <c r="BV76">
         <v>55</v>
       </c>
-      <c r="BX76" s="130">
+      <c r="BX76" s="122">
         <v>42225</v>
       </c>
-      <c r="CB76" s="130">
+      <c r="CB76" s="122">
         <v>42224</v>
       </c>
-      <c r="CC76" s="130">
+      <c r="CC76" s="122">
         <v>42264</v>
       </c>
     </row>
@@ -42892,16 +42864,16 @@
         <v/>
       </c>
       <c r="AE77" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP77" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ77" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV77" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ77">
         <v>101</v>
@@ -42936,13 +42908,13 @@
       <c r="BV77">
         <v>1055</v>
       </c>
-      <c r="BX77" s="130">
+      <c r="BX77" s="122">
         <v>42228</v>
       </c>
-      <c r="CB77" s="130">
+      <c r="CB77" s="122">
         <v>42227</v>
       </c>
-      <c r="CC77" s="130">
+      <c r="CC77" s="122">
         <v>42267</v>
       </c>
     </row>
@@ -43063,16 +43035,16 @@
         <v/>
       </c>
       <c r="AE78" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP78" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ78" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV78" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ78">
         <v>201</v>
@@ -43107,13 +43079,13 @@
       <c r="BV78">
         <v>2055</v>
       </c>
-      <c r="BX78" s="130">
+      <c r="BX78" s="122">
         <v>42231</v>
       </c>
-      <c r="CB78" s="130">
+      <c r="CB78" s="122">
         <v>42230</v>
       </c>
-      <c r="CC78" s="130">
+      <c r="CC78" s="122">
         <v>42270</v>
       </c>
     </row>
@@ -43234,16 +43206,16 @@
         <v/>
       </c>
       <c r="AE79" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP79" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ79" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV79" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ79">
         <v>301</v>
@@ -43278,13 +43250,13 @@
       <c r="BV79">
         <v>3055</v>
       </c>
-      <c r="BX79" s="130">
+      <c r="BX79" s="122">
         <v>42234</v>
       </c>
-      <c r="CB79" s="130">
+      <c r="CB79" s="122">
         <v>42233</v>
       </c>
-      <c r="CC79" s="130">
+      <c r="CC79" s="122">
         <v>42273</v>
       </c>
     </row>
@@ -43405,16 +43377,16 @@
         <v/>
       </c>
       <c r="AE80" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP80" t="s">
         <v>180</v>
       </c>
       <c r="AQ80" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV80" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ80">
         <v>401</v>
@@ -43449,13 +43421,13 @@
       <c r="BV80">
         <v>4055</v>
       </c>
-      <c r="BX80" s="130">
+      <c r="BX80" s="122">
         <v>42237</v>
       </c>
-      <c r="CB80" s="130">
+      <c r="CB80" s="122">
         <v>42236</v>
       </c>
-      <c r="CC80" s="130">
+      <c r="CC80" s="122">
         <v>42276</v>
       </c>
     </row>
@@ -43576,16 +43548,16 @@
         <v/>
       </c>
       <c r="AE81" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP81" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ81" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV81" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ81">
         <v>501</v>
@@ -43620,13 +43592,13 @@
       <c r="BV81">
         <v>5055</v>
       </c>
-      <c r="BX81" s="130">
+      <c r="BX81" s="122">
         <v>42240</v>
       </c>
-      <c r="CB81" s="130">
+      <c r="CB81" s="122">
         <v>42239</v>
       </c>
-      <c r="CC81" s="130">
+      <c r="CC81" s="122">
         <v>42279</v>
       </c>
     </row>
@@ -43747,16 +43719,16 @@
         <v/>
       </c>
       <c r="AE82" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="AP82" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ82" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AV82" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ82">
         <v>601</v>
@@ -43791,13 +43763,13 @@
       <c r="BV82">
         <v>6055</v>
       </c>
-      <c r="BX82" s="130">
+      <c r="BX82" s="122">
         <v>42243</v>
       </c>
-      <c r="CB82" s="130">
+      <c r="CB82" s="122">
         <v>42242</v>
       </c>
-      <c r="CC82" s="130">
+      <c r="CC82" s="122">
         <v>42282</v>
       </c>
     </row>
@@ -43918,16 +43890,16 @@
         <v/>
       </c>
       <c r="AE83" t="s">
+        <v>289</v>
+      </c>
+      <c r="AP83" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ83" t="s">
         <v>298</v>
       </c>
-      <c r="AP83" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ83" t="s">
-        <v>307</v>
-      </c>
       <c r="AV83" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ83">
         <v>1</v>
@@ -43962,13 +43934,13 @@
       <c r="BV83">
         <v>55</v>
       </c>
-      <c r="BX83" s="130">
+      <c r="BX83" s="122">
         <v>42246</v>
       </c>
-      <c r="CB83" s="130">
+      <c r="CB83" s="122">
         <v>42245</v>
       </c>
-      <c r="CC83" s="130">
+      <c r="CC83" s="122">
         <v>42285</v>
       </c>
     </row>
@@ -44089,13 +44061,13 @@
         <v/>
       </c>
       <c r="AE84" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP84" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AV84" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ84">
         <v>101</v>
@@ -44130,13 +44102,13 @@
       <c r="BV84">
         <v>1055</v>
       </c>
-      <c r="BX84" s="130">
+      <c r="BX84" s="122">
         <v>42249</v>
       </c>
-      <c r="CB84" s="130">
+      <c r="CB84" s="122">
         <v>42248</v>
       </c>
-      <c r="CC84" s="130">
+      <c r="CC84" s="122">
         <v>42288</v>
       </c>
     </row>
@@ -44257,16 +44229,16 @@
         <v/>
       </c>
       <c r="AE85" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP85" t="s">
         <v>180</v>
       </c>
       <c r="AQ85" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV85" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ85">
         <v>201</v>
@@ -44301,13 +44273,13 @@
       <c r="BV85">
         <v>2055</v>
       </c>
-      <c r="BX85" s="130">
+      <c r="BX85" s="122">
         <v>42252</v>
       </c>
-      <c r="CB85" s="130">
+      <c r="CB85" s="122">
         <v>42251</v>
       </c>
-      <c r="CC85" s="130">
+      <c r="CC85" s="122">
         <v>42291</v>
       </c>
     </row>
@@ -44428,16 +44400,16 @@
         <v/>
       </c>
       <c r="AE86" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP86" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="AQ86" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="AV86" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ86">
         <v>301</v>
@@ -44472,13 +44444,13 @@
       <c r="BV86">
         <v>3055</v>
       </c>
-      <c r="BX86" s="130">
+      <c r="BX86" s="122">
         <v>42255</v>
       </c>
-      <c r="CB86" s="130">
+      <c r="CB86" s="122">
         <v>42254</v>
       </c>
-      <c r="CC86" s="130">
+      <c r="CC86" s="122">
         <v>42294</v>
       </c>
     </row>
@@ -44599,16 +44571,16 @@
         <v/>
       </c>
       <c r="AE87" t="s">
+        <v>289</v>
+      </c>
+      <c r="AP87" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ87" t="s">
         <v>298</v>
       </c>
-      <c r="AP87" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ87" t="s">
-        <v>307</v>
-      </c>
       <c r="AV87" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ87">
         <v>401</v>
@@ -44643,13 +44615,13 @@
       <c r="BV87">
         <v>4055</v>
       </c>
-      <c r="BX87" s="130">
+      <c r="BX87" s="122">
         <v>42258</v>
       </c>
-      <c r="CB87" s="130">
+      <c r="CB87" s="122">
         <v>42257</v>
       </c>
-      <c r="CC87" s="130">
+      <c r="CC87" s="122">
         <v>42297</v>
       </c>
     </row>
@@ -44770,16 +44742,16 @@
         <v/>
       </c>
       <c r="AE88" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP88" t="s">
         <v>180</v>
       </c>
       <c r="AQ88" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV88" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ88">
         <v>501</v>
@@ -44814,13 +44786,13 @@
       <c r="BV88">
         <v>5055</v>
       </c>
-      <c r="BX88" s="130">
+      <c r="BX88" s="122">
         <v>42261</v>
       </c>
-      <c r="CB88" s="130">
+      <c r="CB88" s="122">
         <v>42260</v>
       </c>
-      <c r="CC88" s="130">
+      <c r="CC88" s="122">
         <v>42300</v>
       </c>
     </row>
@@ -44941,16 +44913,16 @@
         <v/>
       </c>
       <c r="AE89" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP89" t="s">
         <v>180</v>
       </c>
       <c r="AQ89" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV89" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ89">
         <v>601</v>
@@ -44985,13 +44957,13 @@
       <c r="BV89">
         <v>6055</v>
       </c>
-      <c r="BX89" s="130">
+      <c r="BX89" s="122">
         <v>42264</v>
       </c>
-      <c r="CB89" s="130">
+      <c r="CB89" s="122">
         <v>42263</v>
       </c>
-      <c r="CC89" s="130">
+      <c r="CC89" s="122">
         <v>42303</v>
       </c>
     </row>
@@ -45112,16 +45084,16 @@
         <v/>
       </c>
       <c r="AE90" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP90" t="s">
         <v>180</v>
       </c>
       <c r="AQ90" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV90" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ90">
         <v>1</v>
@@ -45156,13 +45128,13 @@
       <c r="BV90">
         <v>55</v>
       </c>
-      <c r="BX90" s="130">
+      <c r="BX90" s="122">
         <v>42267</v>
       </c>
-      <c r="CB90" s="130">
+      <c r="CB90" s="122">
         <v>42266</v>
       </c>
-      <c r="CC90" s="130">
+      <c r="CC90" s="122">
         <v>42306</v>
       </c>
     </row>
@@ -45283,16 +45255,16 @@
         <v/>
       </c>
       <c r="AE91" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP91" t="s">
         <v>180</v>
       </c>
       <c r="AQ91" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AV91" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ91">
         <v>101</v>
@@ -45327,13 +45299,13 @@
       <c r="BV91">
         <v>1055</v>
       </c>
-      <c r="BX91" s="130">
+      <c r="BX91" s="122">
         <v>42270</v>
       </c>
-      <c r="CB91" s="130">
+      <c r="CB91" s="122">
         <v>42269</v>
       </c>
-      <c r="CC91" s="130">
+      <c r="CC91" s="122">
         <v>42309</v>
       </c>
     </row>
@@ -45454,13 +45426,13 @@
         <v/>
       </c>
       <c r="AE92" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AP92" t="s">
         <v>180</v>
       </c>
       <c r="AV92" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ92">
         <v>201</v>
@@ -45495,13 +45467,13 @@
       <c r="BV92">
         <v>2055</v>
       </c>
-      <c r="BX92" s="130">
+      <c r="BX92" s="122">
         <v>42273</v>
       </c>
-      <c r="CB92" s="130">
+      <c r="CB92" s="122">
         <v>42272</v>
       </c>
-      <c r="CC92" s="130">
+      <c r="CC92" s="122">
         <v>42312</v>
       </c>
     </row>
@@ -45622,13 +45594,13 @@
         <v/>
       </c>
       <c r="AE93" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP93" t="s">
         <v>180</v>
       </c>
       <c r="AV93" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="BJ93">
         <v>301</v>
@@ -45663,13 +45635,13 @@
       <c r="BV93">
         <v>3055</v>
       </c>
-      <c r="BX93" s="130">
+      <c r="BX93" s="122">
         <v>42276</v>
       </c>
-      <c r="CB93" s="130">
+      <c r="CB93" s="122">
         <v>42275</v>
       </c>
-      <c r="CC93" s="130">
+      <c r="CC93" s="122">
         <v>42315</v>
       </c>
     </row>
@@ -45790,16 +45762,16 @@
         <v/>
       </c>
       <c r="AE94" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP94" t="s">
         <v>180</v>
       </c>
       <c r="AQ94" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV94" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ94">
         <v>401</v>
@@ -45834,13 +45806,13 @@
       <c r="BV94">
         <v>4055</v>
       </c>
-      <c r="BX94" s="130">
+      <c r="BX94" s="122">
         <v>42279</v>
       </c>
-      <c r="CB94" s="130">
+      <c r="CB94" s="122">
         <v>42278</v>
       </c>
-      <c r="CC94" s="130">
+      <c r="CC94" s="122">
         <v>42318</v>
       </c>
     </row>
@@ -45961,16 +45933,16 @@
         <v/>
       </c>
       <c r="AE95" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP95" t="s">
         <v>180</v>
       </c>
       <c r="AQ95" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV95" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ95">
         <v>501</v>
@@ -46005,13 +45977,13 @@
       <c r="BV95">
         <v>5055</v>
       </c>
-      <c r="BX95" s="130">
+      <c r="BX95" s="122">
         <v>42282</v>
       </c>
-      <c r="CB95" s="130">
+      <c r="CB95" s="122">
         <v>42281</v>
       </c>
-      <c r="CC95" s="130">
+      <c r="CC95" s="122">
         <v>42321</v>
       </c>
     </row>
@@ -46132,16 +46104,16 @@
         <v/>
       </c>
       <c r="AE96" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP96" t="s">
         <v>180</v>
       </c>
       <c r="AQ96" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV96" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="BJ96">
         <v>601</v>
@@ -46176,13 +46148,13 @@
       <c r="BV96">
         <v>6055</v>
       </c>
-      <c r="BX96" s="130">
+      <c r="BX96" s="122">
         <v>42285</v>
       </c>
-      <c r="CB96" s="130">
+      <c r="CB96" s="122">
         <v>42284</v>
       </c>
-      <c r="CC96" s="130">
+      <c r="CC96" s="122">
         <v>42324</v>
       </c>
     </row>
@@ -46303,16 +46275,16 @@
         <v/>
       </c>
       <c r="AE97" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP97" t="s">
         <v>180</v>
       </c>
       <c r="AQ97" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV97" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ97">
         <v>1</v>
@@ -46347,13 +46319,13 @@
       <c r="BV97">
         <v>55</v>
       </c>
-      <c r="BX97" s="130">
+      <c r="BX97" s="122">
         <v>42288</v>
       </c>
-      <c r="CB97" s="130">
+      <c r="CB97" s="122">
         <v>42287</v>
       </c>
-      <c r="CC97" s="130">
+      <c r="CC97" s="122">
         <v>42327</v>
       </c>
     </row>
@@ -46474,16 +46446,16 @@
         <v/>
       </c>
       <c r="AE98" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP98" t="s">
         <v>180</v>
       </c>
       <c r="AQ98" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="AV98" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ98">
         <v>101</v>
@@ -46518,13 +46490,13 @@
       <c r="BV98">
         <v>1055</v>
       </c>
-      <c r="BX98" s="130">
+      <c r="BX98" s="122">
         <v>42291</v>
       </c>
-      <c r="CB98" s="130">
+      <c r="CB98" s="122">
         <v>42290</v>
       </c>
-      <c r="CC98" s="130">
+      <c r="CC98" s="122">
         <v>42330</v>
       </c>
     </row>
@@ -46645,16 +46617,16 @@
         <v/>
       </c>
       <c r="AE99" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP99" t="s">
         <v>180</v>
       </c>
       <c r="AQ99" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AV99" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="BJ99">
         <v>201</v>
@@ -46689,13 +46661,13 @@
       <c r="BV99">
         <v>2055</v>
       </c>
-      <c r="BX99" s="130">
+      <c r="BX99" s="122">
         <v>42294</v>
       </c>
-      <c r="CB99" s="130">
+      <c r="CB99" s="122">
         <v>42293</v>
       </c>
-      <c r="CC99" s="130">
+      <c r="CC99" s="122">
         <v>42333</v>
       </c>
     </row>
@@ -46816,16 +46788,16 @@
         <v/>
       </c>
       <c r="AE100" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP100" t="s">
         <v>180</v>
       </c>
       <c r="AQ100" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="AV100" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="BJ100">
         <v>301</v>
@@ -46860,13 +46832,13 @@
       <c r="BV100">
         <v>3055</v>
       </c>
-      <c r="BX100" s="130">
+      <c r="BX100" s="122">
         <v>42297</v>
       </c>
-      <c r="CB100" s="130">
+      <c r="CB100" s="122">
         <v>42296</v>
       </c>
-      <c r="CC100" s="130">
+      <c r="CC100" s="122">
         <v>42336</v>
       </c>
     </row>
@@ -46987,16 +46959,16 @@
         <v/>
       </c>
       <c r="AE101" t="s">
+        <v>290</v>
+      </c>
+      <c r="AP101" t="s">
+        <v>292</v>
+      </c>
+      <c r="AQ101" t="s">
         <v>299</v>
       </c>
-      <c r="AP101" t="s">
-        <v>301</v>
-      </c>
-      <c r="AQ101" t="s">
-        <v>308</v>
-      </c>
       <c r="AV101" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ101">
         <v>401</v>
@@ -47031,13 +47003,13 @@
       <c r="BV101">
         <v>4055</v>
       </c>
-      <c r="BX101" s="130">
+      <c r="BX101" s="122">
         <v>42300</v>
       </c>
-      <c r="CB101" s="130">
+      <c r="CB101" s="122">
         <v>42299</v>
       </c>
-      <c r="CC101" s="130">
+      <c r="CC101" s="122">
         <v>42339</v>
       </c>
     </row>
@@ -47158,16 +47130,16 @@
         <v/>
       </c>
       <c r="AE102" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AP102" t="s">
         <v>180</v>
       </c>
       <c r="AQ102" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AV102" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="BJ102">
         <v>501</v>
@@ -47202,13 +47174,13 @@
       <c r="BV102">
         <v>5055</v>
       </c>
-      <c r="BX102" s="130">
+      <c r="BX102" s="122">
         <v>42303</v>
       </c>
-      <c r="CB102" s="130">
+      <c r="CB102" s="122">
         <v>42302</v>
       </c>
-      <c r="CC102" s="130">
+      <c r="CC102" s="122">
         <v>42342</v>
       </c>
     </row>
@@ -47231,7 +47203,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -47294,87 +47266,267 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="121" t="s">
-        <v>268</v>
-      </c>
-      <c r="B2" s="122" t="s">
-        <v>269</v>
-      </c>
-      <c r="C2" s="122" t="s">
-        <v>269</v>
-      </c>
-      <c r="D2" s="122" t="s">
-        <v>269</v>
-      </c>
-      <c r="E2" s="122" t="s">
-        <v>258</v>
-      </c>
-      <c r="F2" s="122" t="s">
-        <v>270</v>
-      </c>
-      <c r="G2" s="122" t="s">
-        <v>271</v>
-      </c>
-      <c r="H2" s="122" t="s">
-        <v>272</v>
-      </c>
-      <c r="I2" s="122" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="123">
-        <v>42369</v>
-      </c>
-      <c r="K2" s="122" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" s="122"/>
-      <c r="M2" s="123">
-        <v>42145</v>
-      </c>
-      <c r="N2" s="124" t="s">
-        <v>74</v>
+      <c r="A2" s="131">
+        <v>0</v>
+      </c>
+      <c r="B2" s="131">
+        <v>0</v>
+      </c>
+      <c r="C2" s="131">
+        <v>0</v>
+      </c>
+      <c r="D2" s="132" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="131">
+        <v>0</v>
+      </c>
+      <c r="F2" s="131">
+        <v>0</v>
+      </c>
+      <c r="G2" s="131">
+        <v>0</v>
+      </c>
+      <c r="H2" s="131">
+        <v>0</v>
+      </c>
+      <c r="I2" s="131">
+        <v>0</v>
+      </c>
+      <c r="J2" s="131">
+        <v>0</v>
+      </c>
+      <c r="K2" s="131">
+        <v>0</v>
+      </c>
+      <c r="L2" s="131">
+        <v>0</v>
+      </c>
+      <c r="M2" s="131">
+        <v>0</v>
+      </c>
+      <c r="N2" s="131">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="125" t="s">
-        <v>273</v>
-      </c>
-      <c r="B3" s="126" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="126" t="s">
-        <v>274</v>
-      </c>
-      <c r="D3" s="126" t="s">
-        <v>274</v>
-      </c>
-      <c r="E3" s="126" t="s">
-        <v>275</v>
-      </c>
-      <c r="F3" s="126" t="s">
-        <v>276</v>
-      </c>
-      <c r="G3" s="126" t="s">
-        <v>271</v>
-      </c>
-      <c r="H3" s="126" t="s">
-        <v>272</v>
-      </c>
-      <c r="I3" s="126" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="127">
-        <v>42369</v>
-      </c>
-      <c r="K3" s="126" t="s">
-        <v>74</v>
-      </c>
-      <c r="L3" s="126"/>
-      <c r="M3" s="127">
-        <v>42145</v>
-      </c>
-      <c r="N3" s="128" t="s">
-        <v>74</v>
+      <c r="A3" s="131">
+        <v>0</v>
+      </c>
+      <c r="B3" s="131">
+        <v>0</v>
+      </c>
+      <c r="C3" s="131">
+        <v>0</v>
+      </c>
+      <c r="D3" s="132" t="s">
+        <v>335</v>
+      </c>
+      <c r="E3" s="131">
+        <v>0</v>
+      </c>
+      <c r="F3" s="131">
+        <v>0</v>
+      </c>
+      <c r="G3" s="131">
+        <v>0</v>
+      </c>
+      <c r="H3" s="131">
+        <v>0</v>
+      </c>
+      <c r="I3" s="131">
+        <v>0</v>
+      </c>
+      <c r="J3" s="131">
+        <v>0</v>
+      </c>
+      <c r="K3" s="131">
+        <v>0</v>
+      </c>
+      <c r="L3" s="131">
+        <v>0</v>
+      </c>
+      <c r="M3" s="131">
+        <v>0</v>
+      </c>
+      <c r="N3" s="131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="131">
+        <v>0</v>
+      </c>
+      <c r="B4" s="131">
+        <v>0</v>
+      </c>
+      <c r="C4" s="131">
+        <v>0</v>
+      </c>
+      <c r="D4" s="132" t="s">
+        <v>333</v>
+      </c>
+      <c r="E4" s="131">
+        <v>0</v>
+      </c>
+      <c r="F4" s="131">
+        <v>0</v>
+      </c>
+      <c r="G4" s="131">
+        <v>0</v>
+      </c>
+      <c r="H4" s="131">
+        <v>0</v>
+      </c>
+      <c r="I4" s="131">
+        <v>0</v>
+      </c>
+      <c r="J4" s="131">
+        <v>0</v>
+      </c>
+      <c r="K4" s="131">
+        <v>0</v>
+      </c>
+      <c r="L4" s="131">
+        <v>0</v>
+      </c>
+      <c r="M4" s="131">
+        <v>0</v>
+      </c>
+      <c r="N4" s="131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="131">
+        <v>0</v>
+      </c>
+      <c r="B5" s="131">
+        <v>0</v>
+      </c>
+      <c r="C5" s="131">
+        <v>0</v>
+      </c>
+      <c r="D5" s="132" t="s">
+        <v>336</v>
+      </c>
+      <c r="E5" s="131">
+        <v>0</v>
+      </c>
+      <c r="F5" s="131">
+        <v>0</v>
+      </c>
+      <c r="G5" s="131">
+        <v>0</v>
+      </c>
+      <c r="H5" s="131">
+        <v>0</v>
+      </c>
+      <c r="I5" s="131">
+        <v>0</v>
+      </c>
+      <c r="J5" s="131">
+        <v>0</v>
+      </c>
+      <c r="K5" s="131">
+        <v>0</v>
+      </c>
+      <c r="L5" s="131">
+        <v>0</v>
+      </c>
+      <c r="M5" s="131">
+        <v>0</v>
+      </c>
+      <c r="N5" s="131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="131">
+        <v>0</v>
+      </c>
+      <c r="B6" s="131">
+        <v>0</v>
+      </c>
+      <c r="C6" s="131">
+        <v>0</v>
+      </c>
+      <c r="D6" s="132" t="s">
+        <v>334</v>
+      </c>
+      <c r="E6" s="131">
+        <v>0</v>
+      </c>
+      <c r="F6" s="131">
+        <v>0</v>
+      </c>
+      <c r="G6" s="131">
+        <v>0</v>
+      </c>
+      <c r="H6" s="131">
+        <v>0</v>
+      </c>
+      <c r="I6" s="131">
+        <v>0</v>
+      </c>
+      <c r="J6" s="131">
+        <v>0</v>
+      </c>
+      <c r="K6" s="131">
+        <v>0</v>
+      </c>
+      <c r="L6" s="131">
+        <v>0</v>
+      </c>
+      <c r="M6" s="131">
+        <v>0</v>
+      </c>
+      <c r="N6" s="131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="131">
+        <v>0</v>
+      </c>
+      <c r="B7" s="131">
+        <v>0</v>
+      </c>
+      <c r="C7" s="131">
+        <v>0</v>
+      </c>
+      <c r="D7" s="132" t="s">
+        <v>337</v>
+      </c>
+      <c r="E7" s="131">
+        <v>0</v>
+      </c>
+      <c r="F7" s="131">
+        <v>0</v>
+      </c>
+      <c r="G7" s="131">
+        <v>0</v>
+      </c>
+      <c r="H7" s="131">
+        <v>0</v>
+      </c>
+      <c r="I7" s="131">
+        <v>0</v>
+      </c>
+      <c r="J7" s="131">
+        <v>0</v>
+      </c>
+      <c r="K7" s="131">
+        <v>0</v>
+      </c>
+      <c r="L7" s="131">
+        <v>0</v>
+      </c>
+      <c r="M7" s="131">
+        <v>0</v>
+      </c>
+      <c r="N7" s="131">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -47403,7 +47555,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="70"/>
-      <c r="B4" s="164">
+      <c r="B4" s="158">
         <v>2015</v>
       </c>
     </row>
@@ -47411,7 +47563,7 @@
       <c r="A5" s="70" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="164">
+      <c r="B5" s="158">
         <v>2015</v>
       </c>
     </row>
